--- a/simple_simulation/eepf_plot_50.xlsx
+++ b/simple_simulation/eepf_plot_50.xlsx
@@ -663,7 +663,7 @@
         <v>0.2329</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>0.1127339</v>
+        <v>0.1151691</v>
       </c>
     </row>
     <row r="14">
@@ -671,7 +671,7 @@
         <v>0.5988</v>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.1092348</v>
+        <v>0.1096888</v>
       </c>
     </row>
     <row r="15">
@@ -679,7 +679,7 @@
         <v>0.9646</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>0.101229</v>
+        <v>0.1011442</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +687,7 @@
         <v>1.3304</v>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.09297333000000001</v>
+        <v>0.09280173999999999</v>
       </c>
     </row>
     <row r="17">
@@ -695,7 +695,7 @@
         <v>1.6963</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>0.08695306999999999</v>
+        <v>0.08491606</v>
       </c>
     </row>
     <row r="18">
@@ -703,7 +703,7 @@
         <v>2.0621</v>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.07890737</v>
+        <v>0.07945355</v>
       </c>
     </row>
     <row r="19">
@@ -711,7 +711,7 @@
         <v>2.4279</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>0.0728915</v>
+        <v>0.07291735000000001</v>
       </c>
     </row>
     <row r="20">
@@ -719,7 +719,7 @@
         <v>2.7938</v>
       </c>
       <c r="B20" s="9" t="n">
-        <v>0.06728212</v>
+        <v>0.0680255</v>
       </c>
     </row>
     <row r="21">
@@ -727,7 +727,7 @@
         <v>3.1596</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>0.06263926</v>
+        <v>0.06266961</v>
       </c>
     </row>
     <row r="22">
@@ -735,7 +735,7 @@
         <v>3.5254</v>
       </c>
       <c r="B22" s="9" t="n">
-        <v>0.05817858</v>
+        <v>0.05832175</v>
       </c>
     </row>
     <row r="23">
@@ -743,7 +743,7 @@
         <v>3.8912</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>0.05372131</v>
+        <v>0.05396241</v>
       </c>
     </row>
     <row r="24">
@@ -751,7 +751,7 @@
         <v>4.2571</v>
       </c>
       <c r="B24" s="9" t="n">
-        <v>0.04934689</v>
+        <v>0.04925609</v>
       </c>
     </row>
     <row r="25">
@@ -759,7 +759,7 @@
         <v>4.6229</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>0.04620779</v>
+        <v>0.04580698</v>
       </c>
     </row>
     <row r="26">
@@ -767,7 +767,7 @@
         <v>4.9887</v>
       </c>
       <c r="B26" s="9" t="n">
-        <v>0.04307607</v>
+        <v>0.04251213</v>
       </c>
     </row>
     <row r="27">
@@ -775,7 +775,7 @@
         <v>5.3546</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>0.03959465</v>
+        <v>0.03934945</v>
       </c>
     </row>
     <row r="28">
@@ -783,7 +783,7 @@
         <v>5.7204</v>
       </c>
       <c r="B28" s="9" t="n">
-        <v>0.03683277</v>
+        <v>0.03688484</v>
       </c>
     </row>
     <row r="29">
@@ -791,7 +791,7 @@
         <v>6.0862</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>0.03415176</v>
+        <v>0.03401831</v>
       </c>
     </row>
     <row r="30">
@@ -799,7 +799,7 @@
         <v>6.4521</v>
       </c>
       <c r="B30" s="9" t="n">
-        <v>0.03142275</v>
+        <v>0.03152634</v>
       </c>
     </row>
     <row r="31">
@@ -807,7 +807,7 @@
         <v>6.8179</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>0.02896182</v>
+        <v>0.02902703</v>
       </c>
     </row>
     <row r="32">
@@ -815,7 +815,7 @@
         <v>7.1837</v>
       </c>
       <c r="B32" s="9" t="n">
-        <v>0.02676572</v>
+        <v>0.02693607</v>
       </c>
     </row>
     <row r="33">
@@ -823,7 +823,7 @@
         <v>7.5496</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>0.02503823</v>
+        <v>0.0248232</v>
       </c>
     </row>
     <row r="34">
@@ -831,7 +831,7 @@
         <v>7.9154</v>
       </c>
       <c r="B34" s="9" t="n">
-        <v>0.02294421</v>
+        <v>0.02311112</v>
       </c>
     </row>
     <row r="35">
@@ -839,7 +839,7 @@
         <v>8.2812</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>0.02109636</v>
+        <v>0.02122426</v>
       </c>
     </row>
     <row r="36">
@@ -847,7 +847,7 @@
         <v>8.6471</v>
       </c>
       <c r="B36" s="9" t="n">
-        <v>0.01938826</v>
+        <v>0.01948866</v>
       </c>
     </row>
     <row r="37">
@@ -855,7 +855,7 @@
         <v>9.0129</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>0.01778849</v>
+        <v>0.01800795</v>
       </c>
     </row>
     <row r="38">
@@ -863,7 +863,7 @@
         <v>9.3788</v>
       </c>
       <c r="B38" s="9" t="n">
-        <v>0.01635656</v>
+        <v>0.01652575</v>
       </c>
     </row>
     <row r="39">
@@ -871,7 +871,7 @@
         <v>9.7446</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>0.01505243</v>
+        <v>0.01515833</v>
       </c>
     </row>
     <row r="40">
@@ -879,7 +879,7 @@
         <v>10.1104</v>
       </c>
       <c r="B40" s="9" t="n">
-        <v>0.01368361</v>
+        <v>0.01386963</v>
       </c>
     </row>
     <row r="41">
@@ -887,7 +887,7 @@
         <v>10.4763</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.01250596</v>
+        <v>0.01251173</v>
       </c>
     </row>
     <row r="42">
@@ -895,7 +895,7 @@
         <v>10.8421</v>
       </c>
       <c r="B42" s="9" t="n">
-        <v>0.0114123</v>
+        <v>0.01139333</v>
       </c>
     </row>
     <row r="43">
@@ -903,7 +903,7 @@
         <v>11.2079</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>0.0103461</v>
+        <v>0.01030612</v>
       </c>
     </row>
     <row r="44">
@@ -911,7 +911,7 @@
         <v>11.5738</v>
       </c>
       <c r="B44" s="9" t="n">
-        <v>0.009251323000000001</v>
+        <v>0.009308637999999999</v>
       </c>
     </row>
     <row r="45">
@@ -919,7 +919,7 @@
         <v>11.9396</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>0.008221693</v>
+        <v>0.008203039000000001</v>
       </c>
     </row>
     <row r="46">
@@ -927,7 +927,7 @@
         <v>12.3054</v>
       </c>
       <c r="B46" s="9" t="n">
-        <v>0.007281871</v>
+        <v>0.007301025</v>
       </c>
     </row>
     <row r="47">
@@ -935,7 +935,7 @@
         <v>12.6713</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>0.006319353</v>
+        <v>0.006344912</v>
       </c>
     </row>
     <row r="48">
@@ -943,7 +943,7 @@
         <v>13.0371</v>
       </c>
       <c r="B48" s="9" t="n">
-        <v>0.005476844</v>
+        <v>0.005440954</v>
       </c>
     </row>
     <row r="49">
@@ -951,7 +951,7 @@
         <v>13.4029</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>0.0048061</v>
+        <v>0.004815799</v>
       </c>
     </row>
     <row r="50">
@@ -959,7 +959,7 @@
         <v>13.7688</v>
       </c>
       <c r="B50" s="9" t="n">
-        <v>0.004198731</v>
+        <v>0.004098078</v>
       </c>
     </row>
     <row r="51">
@@ -967,7 +967,7 @@
         <v>14.1346</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>0.003726042</v>
+        <v>0.003649953</v>
       </c>
     </row>
     <row r="52">
@@ -975,7 +975,7 @@
         <v>14.5004</v>
       </c>
       <c r="B52" s="9" t="n">
-        <v>0.003281687</v>
+        <v>0.003238296</v>
       </c>
     </row>
     <row r="53">
@@ -983,7 +983,7 @@
         <v>14.8663</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>0.00284845</v>
+        <v>0.002829778</v>
       </c>
     </row>
     <row r="54">
@@ -991,7 +991,7 @@
         <v>15.2321</v>
       </c>
       <c r="B54" s="9" t="n">
-        <v>0.002469341</v>
+        <v>0.002411704</v>
       </c>
     </row>
     <row r="55">
@@ -999,7 +999,7 @@
         <v>15.5979</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>0.002153825</v>
+        <v>0.00210292</v>
       </c>
     </row>
     <row r="56">
@@ -1007,7 +1007,7 @@
         <v>15.9638</v>
       </c>
       <c r="B56" s="9" t="n">
-        <v>0.001813746</v>
+        <v>0.001835299</v>
       </c>
     </row>
     <row r="57">
@@ -1015,7 +1015,7 @@
         <v>16.3296</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>0.001576406</v>
+        <v>0.001562299</v>
       </c>
     </row>
     <row r="58">
@@ -1023,7 +1023,7 @@
         <v>16.6954</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>0.001381577</v>
+        <v>0.001347441</v>
       </c>
     </row>
     <row r="59">
@@ -1031,7 +1031,7 @@
         <v>17.0613</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>0.001165378</v>
+        <v>0.001115072</v>
       </c>
     </row>
     <row r="60">
@@ -1039,7 +1039,7 @@
         <v>17.4271</v>
       </c>
       <c r="B60" s="9" t="n">
-        <v>0.0009695555</v>
+        <v>0.0009215959</v>
       </c>
     </row>
     <row r="61">
@@ -1047,7 +1047,7 @@
         <v>17.7929</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>0.0008268867</v>
+        <v>0.0007718397</v>
       </c>
     </row>
     <row r="62">
@@ -1055,7 +1055,7 @@
         <v>18.1588</v>
       </c>
       <c r="B62" s="9" t="n">
-        <v>0.0006619866</v>
+        <v>0.0006446410000000001</v>
       </c>
     </row>
     <row r="63">
@@ -1063,7 +1063,7 @@
         <v>18.5246</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>0.0005239795</v>
+        <v>0.0005571662</v>
       </c>
     </row>
     <row r="64">
@@ -1071,7 +1071,7 @@
         <v>18.8904</v>
       </c>
       <c r="B64" s="9" t="n">
-        <v>0.0004422728</v>
+        <v>0.0004496503</v>
       </c>
     </row>
     <row r="65">
@@ -1079,7 +1079,7 @@
         <v>19.2563</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>0.0003648222</v>
+        <v>0.0003703874</v>
       </c>
     </row>
     <row r="66">
@@ -1087,7 +1087,7 @@
         <v>19.6221</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>0.0003046822</v>
+        <v>0.0003146186</v>
       </c>
     </row>
     <row r="67">
@@ -1095,7 +1095,7 @@
         <v>19.9879</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>0.000257943</v>
+        <v>0.0002557648</v>
       </c>
     </row>
     <row r="68">
@@ -1103,7 +1103,7 @@
         <v>20.3538</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>0.0002164191</v>
+        <v>0.0002065315</v>
       </c>
     </row>
     <row r="69">
@@ -1111,7 +1111,7 @@
         <v>20.7196</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>0.0001592198</v>
+        <v>0.0001731096</v>
       </c>
     </row>
     <row r="70">
@@ -1119,7 +1119,7 @@
         <v>21.0854</v>
       </c>
       <c r="B70" s="9" t="n">
-        <v>0.0001367987</v>
+        <v>0.0001346714</v>
       </c>
     </row>
     <row r="71">
@@ -1127,7 +1127,7 @@
         <v>21.4513</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>0.0001088938</v>
+        <v>0.0001041175</v>
       </c>
     </row>
     <row r="72">
@@ -1135,7 +1135,7 @@
         <v>21.8171</v>
       </c>
       <c r="B72" s="9" t="n">
-        <v>8.862036e-05</v>
+        <v>8.901416e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>802985</t>
+          <t>851105</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
         <v>0.2329</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>0.1235836</v>
+        <v>0.1157213</v>
       </c>
     </row>
     <row r="14">
@@ -1295,7 +1295,7 @@
         <v>0.5988</v>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.1421727</v>
+        <v>0.1364491</v>
       </c>
     </row>
     <row r="15">
@@ -1303,7 +1303,7 @@
         <v>0.9646</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>0.1389067</v>
+        <v>0.1364127</v>
       </c>
     </row>
     <row r="16">
@@ -1311,7 +1311,7 @@
         <v>1.3304</v>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.1308272</v>
+        <v>0.1301215</v>
       </c>
     </row>
     <row r="17">
@@ -1319,7 +1319,7 @@
         <v>1.6963</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>0.1192319</v>
+        <v>0.1199853</v>
       </c>
     </row>
     <row r="18">
@@ -1327,7 +1327,7 @@
         <v>2.0621</v>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.1106342</v>
+        <v>0.1092081</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>2.4279</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>0.1004234</v>
+        <v>0.09665857</v>
       </c>
     </row>
     <row r="20">
@@ -1343,7 +1343,7 @@
         <v>2.7938</v>
       </c>
       <c r="B20" s="9" t="n">
-        <v>0.08973689999999999</v>
+        <v>0.08946527999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1351,7 +1351,7 @@
         <v>3.1596</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>0.07939435</v>
+        <v>0.07790171</v>
       </c>
     </row>
     <row r="22">
@@ -1359,7 +1359,7 @@
         <v>3.5254</v>
       </c>
       <c r="B22" s="9" t="n">
-        <v>0.07104125</v>
+        <v>0.06792968000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1367,7 +1367,7 @@
         <v>3.8912</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>0.06067308</v>
+        <v>0.05862615</v>
       </c>
     </row>
     <row r="24">
@@ -1375,7 +1375,7 @@
         <v>4.2571</v>
       </c>
       <c r="B24" s="9" t="n">
-        <v>0.05090385</v>
+        <v>0.05080312</v>
       </c>
     </row>
     <row r="25">
@@ -1383,7 +1383,7 @@
         <v>4.6229</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>0.04543186</v>
+        <v>0.0453317</v>
       </c>
     </row>
     <row r="26">
@@ -1391,7 +1391,7 @@
         <v>4.9887</v>
       </c>
       <c r="B26" s="9" t="n">
-        <v>0.04136435</v>
+        <v>0.03994984</v>
       </c>
     </row>
     <row r="27">
@@ -1399,7 +1399,7 @@
         <v>5.3546</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>0.0365251</v>
+        <v>0.034958</v>
       </c>
     </row>
     <row r="28">
@@ -1407,7 +1407,7 @@
         <v>5.7204</v>
       </c>
       <c r="B28" s="9" t="n">
-        <v>0.03177359</v>
+        <v>0.03192144</v>
       </c>
     </row>
     <row r="29">
@@ -1415,7 +1415,7 @@
         <v>6.0862</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>0.02819255</v>
+        <v>0.02798756</v>
       </c>
     </row>
     <row r="30">
@@ -1423,7 +1423,7 @@
         <v>6.4521</v>
       </c>
       <c r="B30" s="9" t="n">
-        <v>0.02458778</v>
+        <v>0.0259884</v>
       </c>
     </row>
     <row r="31">
@@ -1431,7 +1431,7 @@
         <v>6.8179</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>0.02173638</v>
+        <v>0.0237294</v>
       </c>
     </row>
     <row r="32">
@@ -1439,7 +1439,7 @@
         <v>7.1837</v>
       </c>
       <c r="B32" s="9" t="n">
-        <v>0.02014303</v>
+        <v>0.0218284</v>
       </c>
     </row>
     <row r="33">
@@ -1447,7 +1447,7 @@
         <v>7.5496</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>0.0187421</v>
+        <v>0.01985892</v>
       </c>
     </row>
     <row r="34">
@@ -1455,7 +1455,7 @@
         <v>7.9154</v>
       </c>
       <c r="B34" s="9" t="n">
-        <v>0.01711777</v>
+        <v>0.01745786</v>
       </c>
     </row>
     <row r="35">
@@ -1463,7 +1463,7 @@
         <v>8.2812</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>0.0147218</v>
+        <v>0.01602727</v>
       </c>
     </row>
     <row r="36">
@@ -1471,7 +1471,7 @@
         <v>8.6471</v>
       </c>
       <c r="B36" s="9" t="n">
-        <v>0.01397697</v>
+        <v>0.01383161</v>
       </c>
     </row>
     <row r="37">
@@ -1479,7 +1479,7 @@
         <v>9.0129</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>0.01237107</v>
+        <v>0.01284086</v>
       </c>
     </row>
     <row r="38">
@@ -1487,7 +1487,7 @@
         <v>9.3788</v>
       </c>
       <c r="B38" s="9" t="n">
-        <v>0.01125924</v>
+        <v>0.01168887</v>
       </c>
     </row>
     <row r="39">
@@ -1495,7 +1495,7 @@
         <v>9.7446</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>0.009904810999999999</v>
+        <v>0.01056884</v>
       </c>
     </row>
     <row r="40">
@@ -1503,7 +1503,7 @@
         <v>10.1104</v>
       </c>
       <c r="B40" s="9" t="n">
-        <v>0.008858873</v>
+        <v>0.009731488999999999</v>
       </c>
     </row>
     <row r="41">
@@ -1511,7 +1511,7 @@
         <v>10.4763</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.008025678</v>
+        <v>0.008020717</v>
       </c>
     </row>
     <row r="42">
@@ -1519,7 +1519,7 @@
         <v>10.8421</v>
       </c>
       <c r="B42" s="9" t="n">
-        <v>0.007496781</v>
+        <v>0.007587273</v>
       </c>
     </row>
     <row r="43">
@@ -1527,7 +1527,7 @@
         <v>11.2079</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>0.006875543</v>
+        <v>0.006940712</v>
       </c>
     </row>
     <row r="44">
@@ -1535,7 +1535,7 @@
         <v>11.5738</v>
       </c>
       <c r="B44" s="9" t="n">
-        <v>0.006246007</v>
+        <v>0.006170193</v>
       </c>
     </row>
     <row r="45">
@@ -1543,7 +1543,7 @@
         <v>11.9396</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>0.00523414</v>
+        <v>0.005344188</v>
       </c>
     </row>
     <row r="46">
@@ -1551,7 +1551,7 @@
         <v>12.3054</v>
       </c>
       <c r="B46" s="9" t="n">
-        <v>0.004685455</v>
+        <v>0.004793759</v>
       </c>
     </row>
     <row r="47">
@@ -1559,7 +1559,7 @@
         <v>12.6713</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>0.00400353</v>
+        <v>0.004208996</v>
       </c>
     </row>
     <row r="48">
@@ -1567,7 +1567,7 @@
         <v>13.0371</v>
       </c>
       <c r="B48" s="9" t="n">
-        <v>0.003420194</v>
+        <v>0.003973136</v>
       </c>
     </row>
     <row r="49">
@@ -1575,7 +1575,7 @@
         <v>13.4029</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>0.003146018</v>
+        <v>0.003536348</v>
       </c>
     </row>
     <row r="50">
@@ -1583,7 +1583,7 @@
         <v>13.7688</v>
       </c>
       <c r="B50" s="9" t="n">
-        <v>0.002718131</v>
+        <v>0.002926469</v>
       </c>
     </row>
     <row r="51">
@@ -1591,7 +1591,7 @@
         <v>14.1346</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>0.002469666</v>
+        <v>0.002614572</v>
       </c>
     </row>
     <row r="52">
@@ -1599,7 +1599,7 @@
         <v>14.5004</v>
       </c>
       <c r="B52" s="9" t="n">
-        <v>0.002215428</v>
+        <v>0.002311078</v>
       </c>
     </row>
     <row r="53">
@@ -1607,7 +1607,7 @@
         <v>14.8663</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>0.001983786</v>
+        <v>0.002088088</v>
       </c>
     </row>
     <row r="54">
@@ -1615,7 +1615,7 @@
         <v>15.2321</v>
       </c>
       <c r="B54" s="9" t="n">
-        <v>0.001720518</v>
+        <v>0.001945007</v>
       </c>
     </row>
     <row r="55">
@@ -1623,7 +1623,7 @@
         <v>15.5979</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>0.001555228</v>
+        <v>0.001549866</v>
       </c>
     </row>
     <row r="56">
@@ -1631,7 +1631,7 @@
         <v>15.9638</v>
       </c>
       <c r="B56" s="9" t="n">
-        <v>0.001409338</v>
+        <v>0.001393537</v>
       </c>
     </row>
     <row r="57">
@@ -1639,7 +1639,7 @@
         <v>16.3296</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>0.001123542</v>
+        <v>0.001166108</v>
       </c>
     </row>
     <row r="58">
@@ -1647,7 +1647,7 @@
         <v>16.6954</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>0.001000215</v>
+        <v>0.0009619696</v>
       </c>
     </row>
     <row r="59">
@@ -1655,7 +1655,7 @@
         <v>17.0613</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>0.0007600233</v>
+        <v>0.000929796</v>
       </c>
     </row>
     <row r="60">
@@ -1663,7 +1663,7 @@
         <v>17.4271</v>
       </c>
       <c r="B60" s="9" t="n">
-        <v>0.0007095453</v>
+        <v>0.0007335223</v>
       </c>
     </row>
     <row r="61">
@@ -1671,7 +1671,7 @@
         <v>17.7929</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>0.0005818106</v>
+        <v>0.00059936</v>
       </c>
     </row>
     <row r="62">
@@ -1679,7 +1679,7 @@
         <v>18.1588</v>
       </c>
       <c r="B62" s="9" t="n">
-        <v>0.0004839328</v>
+        <v>0.0004838423</v>
       </c>
     </row>
     <row r="63">
@@ -1687,7 +1687,7 @@
         <v>18.5246</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>0.0004189422</v>
+        <v>0.0004237382</v>
       </c>
     </row>
     <row r="64">
@@ -1695,7 +1695,7 @@
         <v>18.8904</v>
       </c>
       <c r="B64" s="9" t="n">
-        <v>0.0003121296</v>
+        <v>0.0003485691</v>
       </c>
     </row>
     <row r="65">
@@ -1703,7 +1703,7 @@
         <v>19.2563</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>0.0002850709</v>
+        <v>0.0003261842</v>
       </c>
     </row>
     <row r="66">
@@ -1711,7 +1711,7 @@
         <v>19.6221</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>0.0002193032</v>
+        <v>0.0002759306</v>
       </c>
     </row>
     <row r="67">
@@ -1719,7 +1719,7 @@
         <v>19.9879</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>0.0001700176</v>
+        <v>0.0002395793</v>
       </c>
     </row>
     <row r="68">
@@ -1727,7 +1727,7 @@
         <v>20.3538</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>0.0001427948</v>
+        <v>0.0001917868</v>
       </c>
     </row>
     <row r="69">
@@ -1735,7 +1735,7 @@
         <v>20.7196</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>0.0001407797</v>
+        <v>0.0001695936</v>
       </c>
     </row>
     <row r="70">
@@ -1743,7 +1743,7 @@
         <v>21.0854</v>
       </c>
       <c r="B70" s="9" t="n">
-        <v>0.000107634</v>
+        <v>0.0001442995</v>
       </c>
     </row>
     <row r="71">
@@ -1751,7 +1751,7 @@
         <v>21.4513</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>0.0001096561</v>
+        <v>0.0001215348</v>
       </c>
     </row>
     <row r="72">
@@ -1759,7 +1759,7 @@
         <v>21.8171</v>
       </c>
       <c r="B72" s="9" t="n">
-        <v>6.348828000000001e-05</v>
+        <v>9.296601e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>47443</t>
+          <t>55919</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
         <v>0.2329</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>0.1886495</v>
+        <v>0.182589</v>
       </c>
     </row>
     <row r="14">
@@ -1919,7 +1919,7 @@
         <v>0.5988</v>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.18593</v>
+        <v>0.2243441</v>
       </c>
     </row>
     <row r="15">
@@ -1927,7 +1927,7 @@
         <v>0.9646</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>0.1792892</v>
+        <v>0.1913165</v>
       </c>
     </row>
     <row r="16">
@@ -1935,7 +1935,7 @@
         <v>1.3304</v>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.1537129</v>
+        <v>0.1813758</v>
       </c>
     </row>
     <row r="17">
@@ -1943,7 +1943,7 @@
         <v>1.6963</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>0.1453519</v>
+        <v>0.1448722</v>
       </c>
     </row>
     <row r="18">
@@ -1951,7 +1951,7 @@
         <v>2.0621</v>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.1324728</v>
+        <v>0.1306781</v>
       </c>
     </row>
     <row r="19">
@@ -1959,7 +1959,7 @@
         <v>2.4279</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>0.1215664</v>
+        <v>0.1183564</v>
       </c>
     </row>
     <row r="20">
@@ -1967,7 +1967,7 @@
         <v>2.7938</v>
       </c>
       <c r="B20" s="9" t="n">
-        <v>0.09526311</v>
+        <v>0.100518</v>
       </c>
     </row>
     <row r="21">
@@ -1975,7 +1975,7 @@
         <v>3.1596</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>0.08506381</v>
+        <v>0.08685902</v>
       </c>
     </row>
     <row r="22">
@@ -1983,7 +1983,7 @@
         <v>3.5254</v>
       </c>
       <c r="B22" s="9" t="n">
-        <v>0.07385706</v>
+        <v>0.0781853</v>
       </c>
     </row>
     <row r="23">
@@ -1991,7 +1991,7 @@
         <v>3.8912</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>0.0608463</v>
+        <v>0.06590221</v>
       </c>
     </row>
     <row r="24">
@@ -1999,7 +1999,7 @@
         <v>4.2571</v>
       </c>
       <c r="B24" s="9" t="n">
-        <v>0.0497228</v>
+        <v>0.05066196</v>
       </c>
     </row>
     <row r="25">
@@ -2007,7 +2007,7 @@
         <v>4.6229</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>0.04677506</v>
+        <v>0.0431257</v>
       </c>
     </row>
     <row r="26">
@@ -2015,7 +2015,7 @@
         <v>4.9887</v>
       </c>
       <c r="B26" s="9" t="n">
-        <v>0.03859119</v>
+        <v>0.03607561</v>
       </c>
     </row>
     <row r="27">
@@ -2023,7 +2023,7 @@
         <v>5.3546</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>0.0309124</v>
+        <v>0.03043965</v>
       </c>
     </row>
     <row r="28">
@@ -2031,7 +2031,7 @@
         <v>5.7204</v>
       </c>
       <c r="B28" s="9" t="n">
-        <v>0.02604545</v>
+        <v>0.02586623</v>
       </c>
     </row>
     <row r="29">
@@ -2039,7 +2039,7 @@
         <v>6.0862</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>0.02564838</v>
+        <v>0.01977553</v>
       </c>
     </row>
     <row r="30">
@@ -2047,7 +2047,7 @@
         <v>6.4521</v>
       </c>
       <c r="B30" s="9" t="n">
-        <v>0.02222865</v>
+        <v>0.01662267</v>
       </c>
     </row>
     <row r="31">
@@ -2055,7 +2055,7 @@
         <v>6.8179</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>0.01583111</v>
+        <v>0.01641443</v>
       </c>
     </row>
     <row r="32">
@@ -2063,7 +2063,7 @@
         <v>7.1837</v>
       </c>
       <c r="B32" s="9" t="n">
-        <v>0.01501348</v>
+        <v>0.01301212</v>
       </c>
     </row>
     <row r="33">
@@ -2071,7 +2071,7 @@
         <v>7.5496</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>0.01006464</v>
+        <v>0.0122116</v>
       </c>
     </row>
     <row r="34">
@@ -2079,7 +2079,7 @@
         <v>7.9154</v>
       </c>
       <c r="B34" s="9" t="n">
-        <v>0.01151199</v>
+        <v>0.01143858</v>
       </c>
     </row>
     <row r="35">
@@ -2087,7 +2087,7 @@
         <v>8.2812</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>0.009027943</v>
+        <v>0.009583057000000001</v>
       </c>
     </row>
     <row r="36">
@@ -2095,7 +2095,7 @@
         <v>8.6471</v>
       </c>
       <c r="B36" s="9" t="n">
-        <v>0.007676552</v>
+        <v>0.008628564999999999</v>
       </c>
     </row>
     <row r="37">
@@ -2103,7 +2103,7 @@
         <v>9.0129</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>0.007672987</v>
+        <v>0.007684787</v>
       </c>
     </row>
     <row r="38">
@@ -2111,7 +2111,7 @@
         <v>9.3788</v>
       </c>
       <c r="B38" s="9" t="n">
-        <v>0.008520992999999999</v>
+        <v>0.008125215</v>
       </c>
     </row>
     <row r="39">
@@ -2119,7 +2119,7 @@
         <v>9.7446</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>0.008470482</v>
+        <v>0.005915662</v>
       </c>
     </row>
     <row r="40">
@@ -2127,7 +2127,7 @@
         <v>10.1104</v>
       </c>
       <c r="B40" s="9" t="n">
-        <v>0.007026688</v>
+        <v>0.00411311</v>
       </c>
     </row>
     <row r="41">
@@ -2135,7 +2135,7 @@
         <v>10.4763</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.00661752</v>
+        <v>0.003677452</v>
       </c>
     </row>
     <row r="42">
@@ -2143,7 +2143,7 @@
         <v>10.8421</v>
       </c>
       <c r="B42" s="9" t="n">
-        <v>0.005435376</v>
+        <v>0.00307934</v>
       </c>
     </row>
     <row r="43">
@@ -2151,7 +2151,7 @@
         <v>11.2079</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>0.004225012</v>
+        <v>0.00365781</v>
       </c>
     </row>
     <row r="44">
@@ -2159,7 +2159,7 @@
         <v>11.5738</v>
       </c>
       <c r="B44" s="9" t="n">
-        <v>0.004497106</v>
+        <v>0.002980416</v>
       </c>
     </row>
     <row r="45">
@@ -2167,7 +2167,7 @@
         <v>11.9396</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>0.004227175</v>
+        <v>0.003274621</v>
       </c>
     </row>
     <row r="46">
@@ -2175,7 +2175,7 @@
         <v>12.3054</v>
       </c>
       <c r="B46" s="9" t="n">
-        <v>0.003406798</v>
+        <v>0.002667036</v>
       </c>
     </row>
     <row r="47">
@@ -2183,7 +2183,7 @@
         <v>12.6713</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>0.003341041</v>
+        <v>0.002986026</v>
       </c>
     </row>
     <row r="48">
@@ -2191,7 +2191,7 @@
         <v>13.0371</v>
       </c>
       <c r="B48" s="9" t="n">
-        <v>0.002814147</v>
+        <v>0.002292662</v>
       </c>
     </row>
     <row r="49">
@@ -2199,7 +2199,7 @@
         <v>13.4029</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>0.002223534</v>
+        <v>0.001806249</v>
       </c>
     </row>
     <row r="50">
@@ -2207,7 +2207,7 @@
         <v>13.7688</v>
       </c>
       <c r="B50" s="9" t="n">
-        <v>0.001742589</v>
+        <v>0.001438874</v>
       </c>
     </row>
     <row r="51">
@@ -2215,7 +2215,7 @@
         <v>14.1346</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>0.002149863</v>
+        <v>0.001719792</v>
       </c>
     </row>
     <row r="52">
@@ -2223,7 +2223,7 @@
         <v>14.5004</v>
       </c>
       <c r="B52" s="9" t="n">
-        <v>0.001425154</v>
+        <v>0.001466419</v>
       </c>
     </row>
     <row r="53">
@@ -2231,7 +2231,7 @@
         <v>14.8663</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>0.001018199</v>
+        <v>0.001524488</v>
       </c>
     </row>
     <row r="54">
@@ -2239,7 +2239,7 @@
         <v>15.2321</v>
       </c>
       <c r="B54" s="9" t="n">
-        <v>0.0006804597</v>
+        <v>0.001029148</v>
       </c>
     </row>
     <row r="55">
@@ -2247,7 +2247,7 @@
         <v>15.5979</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>0.0006870508</v>
+        <v>0.0005085038</v>
       </c>
     </row>
     <row r="56">
@@ -2255,7 +2255,7 @@
         <v>15.9638</v>
       </c>
       <c r="B56" s="9" t="n">
-        <v>0.0005779853</v>
+        <v>0.0005516818</v>
       </c>
     </row>
     <row r="57">
@@ -2263,7 +2263,7 @@
         <v>16.3296</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>0.0006143349</v>
+        <v>0.0007757755</v>
       </c>
     </row>
     <row r="58">
@@ -2271,7 +2271,7 @@
         <v>16.6954</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>0.0005227901</v>
+        <v>0.0007792169</v>
       </c>
     </row>
     <row r="59">
@@ -2279,7 +2279,7 @@
         <v>17.0613</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>0.0003494289</v>
+        <v>0.0003320444</v>
       </c>
     </row>
     <row r="60">
@@ -2287,7 +2287,7 @@
         <v>17.4271</v>
       </c>
       <c r="B60" s="9" t="n">
-        <v>0.0005670166</v>
+        <v>0.0002229384</v>
       </c>
     </row>
     <row r="61">
@@ -2295,7 +2295,7 @@
         <v>17.7929</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>0.0004790366</v>
+        <v>0.0002438593</v>
       </c>
     </row>
     <row r="62">
@@ -2303,7 +2303,7 @@
         <v>18.1588</v>
       </c>
       <c r="B62" s="9" t="n">
-        <v>0.0004606385</v>
+        <v>0.000206906</v>
       </c>
     </row>
     <row r="63">
@@ -2311,7 +2311,7 @@
         <v>18.5246</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>0.0002414474</v>
+        <v>0.0001934721</v>
       </c>
     </row>
     <row r="64">
@@ -2319,7 +2319,7 @@
         <v>18.8904</v>
       </c>
       <c r="B64" s="9" t="n">
-        <v>0.0003984967</v>
+        <v>0.0001352397</v>
       </c>
     </row>
     <row r="65">
@@ -2327,7 +2327,7 @@
         <v>19.2563</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>0.0001710337</v>
+        <v>0.0001004616</v>
       </c>
     </row>
     <row r="66">
@@ -2335,7 +2335,7 @@
         <v>19.6221</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>0.0001042658</v>
+        <v>8.846287e-05</v>
       </c>
     </row>
     <row r="67">
@@ -2343,7 +2343,7 @@
         <v>19.9879</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>7.748038e-05</v>
+        <v>6.573718e-05</v>
       </c>
     </row>
     <row r="68">
@@ -2351,7 +2351,7 @@
         <v>20.3538</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>0.0001663587</v>
+        <v>0.0001085729</v>
       </c>
     </row>
     <row r="69">
@@ -2359,7 +2359,7 @@
         <v>20.7196</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>0.0001141501</v>
+        <v>0.0001721762</v>
       </c>
     </row>
     <row r="70">
@@ -2367,7 +2367,7 @@
         <v>21.0854</v>
       </c>
       <c r="B70" s="9" t="n">
-        <v>0.000150874</v>
+        <v>9.600526e-05</v>
       </c>
     </row>
     <row r="71">
@@ -2375,7 +2375,7 @@
         <v>21.4513</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>2.493033e-05</v>
+        <v>0.0001163349</v>
       </c>
     </row>
     <row r="72">
@@ -2383,7 +2383,7 @@
         <v>21.8171</v>
       </c>
       <c r="B72" s="9" t="n">
-        <v>3.708064e-05</v>
+        <v>4.194742e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2456,19 +2456,19 @@
         <v>0.2329</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>0.1127339</v>
+        <v>0.1151691</v>
       </c>
       <c r="C3" s="8" t="n">
         <v>0.2329</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.1235836</v>
+        <v>0.1157213</v>
       </c>
       <c r="E3" s="8" t="n">
         <v>0.2329</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>0.1886495</v>
+        <v>0.182589</v>
       </c>
     </row>
     <row r="4">
@@ -2476,19 +2476,19 @@
         <v>0.5988</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>0.1092348</v>
+        <v>0.1096888</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>0.5988</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>0.1421727</v>
+        <v>0.1364491</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>0.5988</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>0.18593</v>
+        <v>0.2243441</v>
       </c>
     </row>
     <row r="5">
@@ -2496,19 +2496,19 @@
         <v>0.9646</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.101229</v>
+        <v>0.1011442</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>0.9646</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.1389067</v>
+        <v>0.1364127</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>0.9646</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>0.1792892</v>
+        <v>0.1913165</v>
       </c>
     </row>
     <row r="6">
@@ -2516,19 +2516,19 @@
         <v>1.3304</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>0.09297333000000001</v>
+        <v>0.09280173999999999</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>1.3304</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>0.1308272</v>
+        <v>0.1301215</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>1.3304</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>0.1537129</v>
+        <v>0.1813758</v>
       </c>
     </row>
     <row r="7">
@@ -2536,19 +2536,19 @@
         <v>1.6963</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>0.08695306999999999</v>
+        <v>0.08491606</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>1.6963</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.1192319</v>
+        <v>0.1199853</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>1.6963</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>0.1453519</v>
+        <v>0.1448722</v>
       </c>
     </row>
     <row r="8">
@@ -2556,19 +2556,19 @@
         <v>2.0621</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>0.07890737</v>
+        <v>0.07945355</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>2.0621</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0.1106342</v>
+        <v>0.1092081</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2.0621</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>0.1324728</v>
+        <v>0.1306781</v>
       </c>
     </row>
     <row r="9">
@@ -2576,19 +2576,19 @@
         <v>2.4279</v>
       </c>
       <c r="B9" s="9" t="n">
-        <v>0.0728915</v>
+        <v>0.07291735000000001</v>
       </c>
       <c r="C9" s="8" t="n">
         <v>2.4279</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.1004234</v>
+        <v>0.09665857</v>
       </c>
       <c r="E9" s="8" t="n">
         <v>2.4279</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>0.1215664</v>
+        <v>0.1183564</v>
       </c>
     </row>
     <row r="10">
@@ -2596,19 +2596,19 @@
         <v>2.7938</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.06728212</v>
+        <v>0.0680255</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>2.7938</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0.08973689999999999</v>
+        <v>0.08946527999999999</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>2.7938</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>0.09526311</v>
+        <v>0.100518</v>
       </c>
     </row>
     <row r="11">
@@ -2616,19 +2616,19 @@
         <v>3.1596</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>0.06263926</v>
+        <v>0.06266961</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>3.1596</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.07939435</v>
+        <v>0.07790171</v>
       </c>
       <c r="E11" s="8" t="n">
         <v>3.1596</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>0.08506381</v>
+        <v>0.08685902</v>
       </c>
     </row>
     <row r="12">
@@ -2636,19 +2636,19 @@
         <v>3.5254</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>0.05817858</v>
+        <v>0.05832175</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>3.5254</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.07104125</v>
+        <v>0.06792968000000001</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>3.5254</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>0.07385706</v>
+        <v>0.0781853</v>
       </c>
     </row>
     <row r="13">
@@ -2656,19 +2656,19 @@
         <v>3.8912</v>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.05372131</v>
+        <v>0.05396241</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>3.8912</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.06067308</v>
+        <v>0.05862615</v>
       </c>
       <c r="E13" s="8" t="n">
         <v>3.8912</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>0.0608463</v>
+        <v>0.06590221</v>
       </c>
     </row>
     <row r="14">
@@ -2676,19 +2676,19 @@
         <v>4.2571</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>0.04934689</v>
+        <v>0.04925609</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>4.2571</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.05090385</v>
+        <v>0.05080312</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>4.2571</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0.0497228</v>
+        <v>0.05066196</v>
       </c>
     </row>
     <row r="15">
@@ -2696,19 +2696,19 @@
         <v>4.6229</v>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.04620779</v>
+        <v>0.04580698</v>
       </c>
       <c r="C15" s="8" t="n">
         <v>4.6229</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.04543186</v>
+        <v>0.0453317</v>
       </c>
       <c r="E15" s="8" t="n">
         <v>4.6229</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>0.04677506</v>
+        <v>0.0431257</v>
       </c>
     </row>
     <row r="16">
@@ -2716,19 +2716,19 @@
         <v>4.9887</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>0.04307607</v>
+        <v>0.04251213</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>4.9887</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.04136435</v>
+        <v>0.03994984</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>4.9887</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>0.03859119</v>
+        <v>0.03607561</v>
       </c>
     </row>
     <row r="17">
@@ -2736,19 +2736,19 @@
         <v>5.3546</v>
       </c>
       <c r="B17" s="9" t="n">
-        <v>0.03959465</v>
+        <v>0.03934945</v>
       </c>
       <c r="C17" s="8" t="n">
         <v>5.3546</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.0365251</v>
+        <v>0.034958</v>
       </c>
       <c r="E17" s="8" t="n">
         <v>5.3546</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>0.0309124</v>
+        <v>0.03043965</v>
       </c>
     </row>
     <row r="18">
@@ -2756,19 +2756,19 @@
         <v>5.7204</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>0.03683277</v>
+        <v>0.03688484</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>5.7204</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.03177359</v>
+        <v>0.03192144</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>5.7204</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>0.02604545</v>
+        <v>0.02586623</v>
       </c>
     </row>
     <row r="19">
@@ -2776,19 +2776,19 @@
         <v>6.0862</v>
       </c>
       <c r="B19" s="9" t="n">
-        <v>0.03415176</v>
+        <v>0.03401831</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>6.0862</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.02819255</v>
+        <v>0.02798756</v>
       </c>
       <c r="E19" s="8" t="n">
         <v>6.0862</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>0.02564838</v>
+        <v>0.01977553</v>
       </c>
     </row>
     <row r="20">
@@ -2796,19 +2796,19 @@
         <v>6.4521</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>0.03142275</v>
+        <v>0.03152634</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>6.4521</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.02458778</v>
+        <v>0.0259884</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>6.4521</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.02222865</v>
+        <v>0.01662267</v>
       </c>
     </row>
     <row r="21">
@@ -2816,19 +2816,19 @@
         <v>6.8179</v>
       </c>
       <c r="B21" s="9" t="n">
-        <v>0.02896182</v>
+        <v>0.02902703</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>6.8179</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.02173638</v>
+        <v>0.0237294</v>
       </c>
       <c r="E21" s="8" t="n">
         <v>6.8179</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>0.01583111</v>
+        <v>0.01641443</v>
       </c>
     </row>
     <row r="22">
@@ -2836,19 +2836,19 @@
         <v>7.1837</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>0.02676572</v>
+        <v>0.02693607</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>7.1837</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.02014303</v>
+        <v>0.0218284</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>7.1837</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.01501348</v>
+        <v>0.01301212</v>
       </c>
     </row>
     <row r="23">
@@ -2856,19 +2856,19 @@
         <v>7.5496</v>
       </c>
       <c r="B23" s="9" t="n">
-        <v>0.02503823</v>
+        <v>0.0248232</v>
       </c>
       <c r="C23" s="8" t="n">
         <v>7.5496</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.0187421</v>
+        <v>0.01985892</v>
       </c>
       <c r="E23" s="8" t="n">
         <v>7.5496</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>0.01006464</v>
+        <v>0.0122116</v>
       </c>
     </row>
     <row r="24">
@@ -2876,19 +2876,19 @@
         <v>7.9154</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>0.02294421</v>
+        <v>0.02311112</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>7.9154</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.01711777</v>
+        <v>0.01745786</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>7.9154</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.01151199</v>
+        <v>0.01143858</v>
       </c>
     </row>
     <row r="25">
@@ -2896,19 +2896,19 @@
         <v>8.2812</v>
       </c>
       <c r="B25" s="9" t="n">
-        <v>0.02109636</v>
+        <v>0.02122426</v>
       </c>
       <c r="C25" s="8" t="n">
         <v>8.2812</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.0147218</v>
+        <v>0.01602727</v>
       </c>
       <c r="E25" s="8" t="n">
         <v>8.2812</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>0.009027943</v>
+        <v>0.009583057000000001</v>
       </c>
     </row>
     <row r="26">
@@ -2916,19 +2916,19 @@
         <v>8.6471</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>0.01938826</v>
+        <v>0.01948866</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>8.6471</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>0.01397697</v>
+        <v>0.01383161</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>8.6471</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>0.007676552</v>
+        <v>0.008628564999999999</v>
       </c>
     </row>
     <row r="27">
@@ -2936,19 +2936,19 @@
         <v>9.0129</v>
       </c>
       <c r="B27" s="9" t="n">
-        <v>0.01778849</v>
+        <v>0.01800795</v>
       </c>
       <c r="C27" s="8" t="n">
         <v>9.0129</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.01237107</v>
+        <v>0.01284086</v>
       </c>
       <c r="E27" s="8" t="n">
         <v>9.0129</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>0.007672987</v>
+        <v>0.007684787</v>
       </c>
     </row>
     <row r="28">
@@ -2956,19 +2956,19 @@
         <v>9.3788</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>0.01635656</v>
+        <v>0.01652575</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>9.3788</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>0.01125924</v>
+        <v>0.01168887</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>9.3788</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>0.008520992999999999</v>
+        <v>0.008125215</v>
       </c>
     </row>
     <row r="29">
@@ -2976,19 +2976,19 @@
         <v>9.7446</v>
       </c>
       <c r="B29" s="9" t="n">
-        <v>0.01505243</v>
+        <v>0.01515833</v>
       </c>
       <c r="C29" s="8" t="n">
         <v>9.7446</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.009904810999999999</v>
+        <v>0.01056884</v>
       </c>
       <c r="E29" s="8" t="n">
         <v>9.7446</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>0.008470482</v>
+        <v>0.005915662</v>
       </c>
     </row>
     <row r="30">
@@ -2996,19 +2996,19 @@
         <v>10.1104</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>0.01368361</v>
+        <v>0.01386963</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>10.1104</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>0.008858873</v>
+        <v>0.009731488999999999</v>
       </c>
       <c r="E30" s="6" t="n">
         <v>10.1104</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>0.007026688</v>
+        <v>0.00411311</v>
       </c>
     </row>
     <row r="31">
@@ -3016,19 +3016,19 @@
         <v>10.4763</v>
       </c>
       <c r="B31" s="9" t="n">
-        <v>0.01250596</v>
+        <v>0.01251173</v>
       </c>
       <c r="C31" s="8" t="n">
         <v>10.4763</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.008025678</v>
+        <v>0.008020717</v>
       </c>
       <c r="E31" s="8" t="n">
         <v>10.4763</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>0.00661752</v>
+        <v>0.003677452</v>
       </c>
     </row>
     <row r="32">
@@ -3036,19 +3036,19 @@
         <v>10.8421</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>0.0114123</v>
+        <v>0.01139333</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>10.8421</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>0.007496781</v>
+        <v>0.007587273</v>
       </c>
       <c r="E32" s="6" t="n">
         <v>10.8421</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>0.005435376</v>
+        <v>0.00307934</v>
       </c>
     </row>
     <row r="33">
@@ -3056,19 +3056,19 @@
         <v>11.2079</v>
       </c>
       <c r="B33" s="9" t="n">
-        <v>0.0103461</v>
+        <v>0.01030612</v>
       </c>
       <c r="C33" s="8" t="n">
         <v>11.2079</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.006875543</v>
+        <v>0.006940712</v>
       </c>
       <c r="E33" s="8" t="n">
         <v>11.2079</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>0.004225012</v>
+        <v>0.00365781</v>
       </c>
     </row>
     <row r="34">
@@ -3076,19 +3076,19 @@
         <v>11.5738</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>0.009251323000000001</v>
+        <v>0.009308637999999999</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>11.5738</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>0.006246007</v>
+        <v>0.006170193</v>
       </c>
       <c r="E34" s="6" t="n">
         <v>11.5738</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>0.004497106</v>
+        <v>0.002980416</v>
       </c>
     </row>
     <row r="35">
@@ -3096,19 +3096,19 @@
         <v>11.9396</v>
       </c>
       <c r="B35" s="9" t="n">
-        <v>0.008221693</v>
+        <v>0.008203039000000001</v>
       </c>
       <c r="C35" s="8" t="n">
         <v>11.9396</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.00523414</v>
+        <v>0.005344188</v>
       </c>
       <c r="E35" s="8" t="n">
         <v>11.9396</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>0.004227175</v>
+        <v>0.003274621</v>
       </c>
     </row>
     <row r="36">
@@ -3116,19 +3116,19 @@
         <v>12.3054</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>0.007281871</v>
+        <v>0.007301025</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>12.3054</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>0.004685455</v>
+        <v>0.004793759</v>
       </c>
       <c r="E36" s="6" t="n">
         <v>12.3054</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>0.003406798</v>
+        <v>0.002667036</v>
       </c>
     </row>
     <row r="37">
@@ -3136,19 +3136,19 @@
         <v>12.6713</v>
       </c>
       <c r="B37" s="9" t="n">
-        <v>0.006319353</v>
+        <v>0.006344912</v>
       </c>
       <c r="C37" s="8" t="n">
         <v>12.6713</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.00400353</v>
+        <v>0.004208996</v>
       </c>
       <c r="E37" s="8" t="n">
         <v>12.6713</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>0.003341041</v>
+        <v>0.002986026</v>
       </c>
     </row>
     <row r="38">
@@ -3156,19 +3156,19 @@
         <v>13.0371</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>0.005476844</v>
+        <v>0.005440954</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>13.0371</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>0.003420194</v>
+        <v>0.003973136</v>
       </c>
       <c r="E38" s="6" t="n">
         <v>13.0371</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>0.002814147</v>
+        <v>0.002292662</v>
       </c>
     </row>
     <row r="39">
@@ -3176,19 +3176,19 @@
         <v>13.4029</v>
       </c>
       <c r="B39" s="9" t="n">
-        <v>0.0048061</v>
+        <v>0.004815799</v>
       </c>
       <c r="C39" s="8" t="n">
         <v>13.4029</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.003146018</v>
+        <v>0.003536348</v>
       </c>
       <c r="E39" s="8" t="n">
         <v>13.4029</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>0.002223534</v>
+        <v>0.001806249</v>
       </c>
     </row>
     <row r="40">
@@ -3196,19 +3196,19 @@
         <v>13.7688</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>0.004198731</v>
+        <v>0.004098078</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>13.7688</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>0.002718131</v>
+        <v>0.002926469</v>
       </c>
       <c r="E40" s="6" t="n">
         <v>13.7688</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>0.001742589</v>
+        <v>0.001438874</v>
       </c>
     </row>
     <row r="41">
@@ -3216,19 +3216,19 @@
         <v>14.1346</v>
       </c>
       <c r="B41" s="9" t="n">
-        <v>0.003726042</v>
+        <v>0.003649953</v>
       </c>
       <c r="C41" s="8" t="n">
         <v>14.1346</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.002469666</v>
+        <v>0.002614572</v>
       </c>
       <c r="E41" s="8" t="n">
         <v>14.1346</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>0.002149863</v>
+        <v>0.001719792</v>
       </c>
     </row>
     <row r="42">
@@ -3236,19 +3236,19 @@
         <v>14.5004</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>0.003281687</v>
+        <v>0.003238296</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>14.5004</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>0.002215428</v>
+        <v>0.002311078</v>
       </c>
       <c r="E42" s="6" t="n">
         <v>14.5004</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>0.001425154</v>
+        <v>0.001466419</v>
       </c>
     </row>
     <row r="43">
@@ -3256,19 +3256,19 @@
         <v>14.8663</v>
       </c>
       <c r="B43" s="9" t="n">
-        <v>0.00284845</v>
+        <v>0.002829778</v>
       </c>
       <c r="C43" s="8" t="n">
         <v>14.8663</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.001983786</v>
+        <v>0.002088088</v>
       </c>
       <c r="E43" s="8" t="n">
         <v>14.8663</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>0.001018199</v>
+        <v>0.001524488</v>
       </c>
     </row>
     <row r="44">
@@ -3276,19 +3276,19 @@
         <v>15.2321</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>0.002469341</v>
+        <v>0.002411704</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>15.2321</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>0.001720518</v>
+        <v>0.001945007</v>
       </c>
       <c r="E44" s="6" t="n">
         <v>15.2321</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>0.0006804597</v>
+        <v>0.001029148</v>
       </c>
     </row>
     <row r="45">
@@ -3296,19 +3296,19 @@
         <v>15.5979</v>
       </c>
       <c r="B45" s="9" t="n">
-        <v>0.002153825</v>
+        <v>0.00210292</v>
       </c>
       <c r="C45" s="8" t="n">
         <v>15.5979</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.001555228</v>
+        <v>0.001549866</v>
       </c>
       <c r="E45" s="8" t="n">
         <v>15.5979</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>0.0006870508</v>
+        <v>0.0005085038</v>
       </c>
     </row>
     <row r="46">
@@ -3316,19 +3316,19 @@
         <v>15.9638</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>0.001813746</v>
+        <v>0.001835299</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>15.9638</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>0.001409338</v>
+        <v>0.001393537</v>
       </c>
       <c r="E46" s="6" t="n">
         <v>15.9638</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>0.0005779853</v>
+        <v>0.0005516818</v>
       </c>
     </row>
     <row r="47">
@@ -3336,19 +3336,19 @@
         <v>16.3296</v>
       </c>
       <c r="B47" s="9" t="n">
-        <v>0.001576406</v>
+        <v>0.001562299</v>
       </c>
       <c r="C47" s="8" t="n">
         <v>16.3296</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.001123542</v>
+        <v>0.001166108</v>
       </c>
       <c r="E47" s="8" t="n">
         <v>16.3296</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>0.0006143349</v>
+        <v>0.0007757755</v>
       </c>
     </row>
     <row r="48">
@@ -3356,19 +3356,19 @@
         <v>16.6954</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>0.001381577</v>
+        <v>0.001347441</v>
       </c>
       <c r="C48" s="6" t="n">
         <v>16.6954</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>0.001000215</v>
+        <v>0.0009619696</v>
       </c>
       <c r="E48" s="6" t="n">
         <v>16.6954</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>0.0005227901</v>
+        <v>0.0007792169</v>
       </c>
     </row>
     <row r="49">
@@ -3376,19 +3376,19 @@
         <v>17.0613</v>
       </c>
       <c r="B49" s="9" t="n">
-        <v>0.001165378</v>
+        <v>0.001115072</v>
       </c>
       <c r="C49" s="8" t="n">
         <v>17.0613</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.0007600233</v>
+        <v>0.000929796</v>
       </c>
       <c r="E49" s="8" t="n">
         <v>17.0613</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>0.0003494289</v>
+        <v>0.0003320444</v>
       </c>
     </row>
     <row r="50">
@@ -3396,19 +3396,19 @@
         <v>17.4271</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>0.0009695555</v>
+        <v>0.0009215959</v>
       </c>
       <c r="C50" s="6" t="n">
         <v>17.4271</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>0.0007095453</v>
+        <v>0.0007335223</v>
       </c>
       <c r="E50" s="6" t="n">
         <v>17.4271</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>0.0005670166</v>
+        <v>0.0002229384</v>
       </c>
     </row>
     <row r="51">
@@ -3416,19 +3416,19 @@
         <v>17.7929</v>
       </c>
       <c r="B51" s="9" t="n">
-        <v>0.0008268867</v>
+        <v>0.0007718397</v>
       </c>
       <c r="C51" s="8" t="n">
         <v>17.7929</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.0005818106</v>
+        <v>0.00059936</v>
       </c>
       <c r="E51" s="8" t="n">
         <v>17.7929</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>0.0004790366</v>
+        <v>0.0002438593</v>
       </c>
     </row>
     <row r="52">
@@ -3436,19 +3436,19 @@
         <v>18.1588</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>0.0006619866</v>
+        <v>0.0006446410000000001</v>
       </c>
       <c r="C52" s="6" t="n">
         <v>18.1588</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>0.0004839328</v>
+        <v>0.0004838423</v>
       </c>
       <c r="E52" s="6" t="n">
         <v>18.1588</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>0.0004606385</v>
+        <v>0.000206906</v>
       </c>
     </row>
     <row r="53">
@@ -3456,19 +3456,19 @@
         <v>18.5246</v>
       </c>
       <c r="B53" s="9" t="n">
-        <v>0.0005239795</v>
+        <v>0.0005571662</v>
       </c>
       <c r="C53" s="8" t="n">
         <v>18.5246</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.0004189422</v>
+        <v>0.0004237382</v>
       </c>
       <c r="E53" s="8" t="n">
         <v>18.5246</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>0.0002414474</v>
+        <v>0.0001934721</v>
       </c>
     </row>
     <row r="54">
@@ -3476,19 +3476,19 @@
         <v>18.8904</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>0.0004422728</v>
+        <v>0.0004496503</v>
       </c>
       <c r="C54" s="6" t="n">
         <v>18.8904</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>0.0003121296</v>
+        <v>0.0003485691</v>
       </c>
       <c r="E54" s="6" t="n">
         <v>18.8904</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>0.0003984967</v>
+        <v>0.0001352397</v>
       </c>
     </row>
     <row r="55">
@@ -3496,19 +3496,19 @@
         <v>19.2563</v>
       </c>
       <c r="B55" s="9" t="n">
-        <v>0.0003648222</v>
+        <v>0.0003703874</v>
       </c>
       <c r="C55" s="8" t="n">
         <v>19.2563</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.0002850709</v>
+        <v>0.0003261842</v>
       </c>
       <c r="E55" s="8" t="n">
         <v>19.2563</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>0.0001710337</v>
+        <v>0.0001004616</v>
       </c>
     </row>
     <row r="56">
@@ -3516,19 +3516,19 @@
         <v>19.6221</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>0.0003046822</v>
+        <v>0.0003146186</v>
       </c>
       <c r="C56" s="6" t="n">
         <v>19.6221</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>0.0002193032</v>
+        <v>0.0002759306</v>
       </c>
       <c r="E56" s="6" t="n">
         <v>19.6221</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>0.0001042658</v>
+        <v>8.846287e-05</v>
       </c>
     </row>
     <row r="57">
@@ -3536,19 +3536,19 @@
         <v>19.9879</v>
       </c>
       <c r="B57" s="9" t="n">
-        <v>0.000257943</v>
+        <v>0.0002557648</v>
       </c>
       <c r="C57" s="8" t="n">
         <v>19.9879</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.0001700176</v>
+        <v>0.0002395793</v>
       </c>
       <c r="E57" s="8" t="n">
         <v>19.9879</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>7.748038e-05</v>
+        <v>6.573718e-05</v>
       </c>
     </row>
     <row r="58">
@@ -3556,19 +3556,19 @@
         <v>20.3538</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>0.0002164191</v>
+        <v>0.0002065315</v>
       </c>
       <c r="C58" s="6" t="n">
         <v>20.3538</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>0.0001427948</v>
+        <v>0.0001917868</v>
       </c>
       <c r="E58" s="6" t="n">
         <v>20.3538</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>0.0001663587</v>
+        <v>0.0001085729</v>
       </c>
     </row>
     <row r="59">
@@ -3576,19 +3576,19 @@
         <v>20.7196</v>
       </c>
       <c r="B59" s="9" t="n">
-        <v>0.0001592198</v>
+        <v>0.0001731096</v>
       </c>
       <c r="C59" s="8" t="n">
         <v>20.7196</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.0001407797</v>
+        <v>0.0001695936</v>
       </c>
       <c r="E59" s="8" t="n">
         <v>20.7196</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>0.0001141501</v>
+        <v>0.0001721762</v>
       </c>
     </row>
     <row r="60">
@@ -3596,19 +3596,19 @@
         <v>21.0854</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>0.0001367987</v>
+        <v>0.0001346714</v>
       </c>
       <c r="C60" s="6" t="n">
         <v>21.0854</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>0.000107634</v>
+        <v>0.0001442995</v>
       </c>
       <c r="E60" s="6" t="n">
         <v>21.0854</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>0.000150874</v>
+        <v>9.600526e-05</v>
       </c>
     </row>
     <row r="61">
@@ -3616,19 +3616,19 @@
         <v>21.4513</v>
       </c>
       <c r="B61" s="9" t="n">
-        <v>0.0001088938</v>
+        <v>0.0001041175</v>
       </c>
       <c r="C61" s="8" t="n">
         <v>21.4513</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.0001096561</v>
+        <v>0.0001215348</v>
       </c>
       <c r="E61" s="8" t="n">
         <v>21.4513</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>2.493033e-05</v>
+        <v>0.0001163349</v>
       </c>
     </row>
     <row r="62">
@@ -3636,19 +3636,19 @@
         <v>21.8171</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>8.862036e-05</v>
+        <v>8.901416e-05</v>
       </c>
       <c r="C62" s="6" t="n">
         <v>21.8171</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>6.348828000000001e-05</v>
+        <v>9.296601e-05</v>
       </c>
       <c r="E62" s="6" t="n">
         <v>21.8171</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>3.708064e-05</v>
+        <v>4.194742e-05</v>
       </c>
     </row>
   </sheetData>

--- a/simple_simulation/eepf_plot_50.xlsx
+++ b/simple_simulation/eepf_plot_50.xlsx
@@ -663,7 +663,7 @@
         <v>0.2329</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>0.1151691</v>
+        <v>0.1193456</v>
       </c>
     </row>
     <row r="14">
@@ -671,7 +671,7 @@
         <v>0.5988</v>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.1096888</v>
+        <v>0.1140152</v>
       </c>
     </row>
     <row r="15">
@@ -679,7 +679,7 @@
         <v>0.9646</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>0.1011442</v>
+        <v>0.1026151</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +687,7 @@
         <v>1.3304</v>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.09280173999999999</v>
+        <v>0.09476811</v>
       </c>
     </row>
     <row r="17">
@@ -695,7 +695,7 @@
         <v>1.6963</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>0.08491606</v>
+        <v>0.08721385</v>
       </c>
     </row>
     <row r="18">
@@ -703,7 +703,7 @@
         <v>2.0621</v>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.07945355</v>
+        <v>0.07952244999999999</v>
       </c>
     </row>
     <row r="19">
@@ -711,7 +711,7 @@
         <v>2.4279</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>0.07291735000000001</v>
+        <v>0.07321133000000001</v>
       </c>
     </row>
     <row r="20">
@@ -719,7 +719,7 @@
         <v>2.7938</v>
       </c>
       <c r="B20" s="9" t="n">
-        <v>0.0680255</v>
+        <v>0.06774012</v>
       </c>
     </row>
     <row r="21">
@@ -727,7 +727,7 @@
         <v>3.1596</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>0.06266961</v>
+        <v>0.06243023</v>
       </c>
     </row>
     <row r="22">
@@ -735,7 +735,7 @@
         <v>3.5254</v>
       </c>
       <c r="B22" s="9" t="n">
-        <v>0.05832175</v>
+        <v>0.05794753</v>
       </c>
     </row>
     <row r="23">
@@ -743,7 +743,7 @@
         <v>3.8912</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>0.05396241</v>
+        <v>0.05377977</v>
       </c>
     </row>
     <row r="24">
@@ -751,7 +751,7 @@
         <v>4.2571</v>
       </c>
       <c r="B24" s="9" t="n">
-        <v>0.04925609</v>
+        <v>0.04907032</v>
       </c>
     </row>
     <row r="25">
@@ -759,7 +759,7 @@
         <v>4.6229</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>0.04580698</v>
+        <v>0.04528294</v>
       </c>
     </row>
     <row r="26">
@@ -767,7 +767,7 @@
         <v>4.9887</v>
       </c>
       <c r="B26" s="9" t="n">
-        <v>0.04251213</v>
+        <v>0.04256852</v>
       </c>
     </row>
     <row r="27">
@@ -775,7 +775,7 @@
         <v>5.3546</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>0.03934945</v>
+        <v>0.03943648</v>
       </c>
     </row>
     <row r="28">
@@ -783,7 +783,7 @@
         <v>5.7204</v>
       </c>
       <c r="B28" s="9" t="n">
-        <v>0.03688484</v>
+        <v>0.03637444</v>
       </c>
     </row>
     <row r="29">
@@ -791,7 +791,7 @@
         <v>6.0862</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>0.03401831</v>
+        <v>0.03374614</v>
       </c>
     </row>
     <row r="30">
@@ -799,7 +799,7 @@
         <v>6.4521</v>
       </c>
       <c r="B30" s="9" t="n">
-        <v>0.03152634</v>
+        <v>0.03112772</v>
       </c>
     </row>
     <row r="31">
@@ -807,7 +807,7 @@
         <v>6.8179</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>0.02902703</v>
+        <v>0.02879163</v>
       </c>
     </row>
     <row r="32">
@@ -815,7 +815,7 @@
         <v>7.1837</v>
       </c>
       <c r="B32" s="9" t="n">
-        <v>0.02693607</v>
+        <v>0.02686982</v>
       </c>
     </row>
     <row r="33">
@@ -823,7 +823,7 @@
         <v>7.5496</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>0.0248232</v>
+        <v>0.02487285</v>
       </c>
     </row>
     <row r="34">
@@ -831,7 +831,7 @@
         <v>7.9154</v>
       </c>
       <c r="B34" s="9" t="n">
-        <v>0.02311112</v>
+        <v>0.0230132</v>
       </c>
     </row>
     <row r="35">
@@ -839,7 +839,7 @@
         <v>8.2812</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>0.02122426</v>
+        <v>0.02109745</v>
       </c>
     </row>
     <row r="36">
@@ -847,7 +847,7 @@
         <v>8.6471</v>
       </c>
       <c r="B36" s="9" t="n">
-        <v>0.01948866</v>
+        <v>0.01935205</v>
       </c>
     </row>
     <row r="37">
@@ -855,7 +855,7 @@
         <v>9.0129</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>0.01800795</v>
+        <v>0.01805519</v>
       </c>
     </row>
     <row r="38">
@@ -863,7 +863,7 @@
         <v>9.3788</v>
       </c>
       <c r="B38" s="9" t="n">
-        <v>0.01652575</v>
+        <v>0.01650989</v>
       </c>
     </row>
     <row r="39">
@@ -871,7 +871,7 @@
         <v>9.7446</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>0.01515833</v>
+        <v>0.0149138</v>
       </c>
     </row>
     <row r="40">
@@ -879,7 +879,7 @@
         <v>10.1104</v>
       </c>
       <c r="B40" s="9" t="n">
-        <v>0.01386963</v>
+        <v>0.01355793</v>
       </c>
     </row>
     <row r="41">
@@ -887,7 +887,7 @@
         <v>10.4763</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.01251173</v>
+        <v>0.0124706</v>
       </c>
     </row>
     <row r="42">
@@ -895,7 +895,7 @@
         <v>10.8421</v>
       </c>
       <c r="B42" s="9" t="n">
-        <v>0.01139333</v>
+        <v>0.01136191</v>
       </c>
     </row>
     <row r="43">
@@ -903,7 +903,7 @@
         <v>11.2079</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>0.01030612</v>
+        <v>0.01017649</v>
       </c>
     </row>
     <row r="44">
@@ -911,7 +911,7 @@
         <v>11.5738</v>
       </c>
       <c r="B44" s="9" t="n">
-        <v>0.009308637999999999</v>
+        <v>0.009110596</v>
       </c>
     </row>
     <row r="45">
@@ -919,7 +919,7 @@
         <v>11.9396</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>0.008203039000000001</v>
+        <v>0.008042179999999999</v>
       </c>
     </row>
     <row r="46">
@@ -927,7 +927,7 @@
         <v>12.3054</v>
       </c>
       <c r="B46" s="9" t="n">
-        <v>0.007301025</v>
+        <v>0.007092552</v>
       </c>
     </row>
     <row r="47">
@@ -935,7 +935,7 @@
         <v>12.6713</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>0.006344912</v>
+        <v>0.006329598</v>
       </c>
     </row>
     <row r="48">
@@ -943,7 +943,7 @@
         <v>13.0371</v>
       </c>
       <c r="B48" s="9" t="n">
-        <v>0.005440954</v>
+        <v>0.005487783</v>
       </c>
     </row>
     <row r="49">
@@ -951,7 +951,7 @@
         <v>13.4029</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>0.004815799</v>
+        <v>0.00480424</v>
       </c>
     </row>
     <row r="50">
@@ -959,7 +959,7 @@
         <v>13.7688</v>
       </c>
       <c r="B50" s="9" t="n">
-        <v>0.004098078</v>
+        <v>0.004153494</v>
       </c>
     </row>
     <row r="51">
@@ -967,7 +967,7 @@
         <v>14.1346</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>0.003649953</v>
+        <v>0.003554152</v>
       </c>
     </row>
     <row r="52">
@@ -975,7 +975,7 @@
         <v>14.5004</v>
       </c>
       <c r="B52" s="9" t="n">
-        <v>0.003238296</v>
+        <v>0.003176313</v>
       </c>
     </row>
     <row r="53">
@@ -983,7 +983,7 @@
         <v>14.8663</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>0.002829778</v>
+        <v>0.002784939</v>
       </c>
     </row>
     <row r="54">
@@ -991,7 +991,7 @@
         <v>15.2321</v>
       </c>
       <c r="B54" s="9" t="n">
-        <v>0.002411704</v>
+        <v>0.002448064</v>
       </c>
     </row>
     <row r="55">
@@ -999,7 +999,7 @@
         <v>15.5979</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>0.00210292</v>
+        <v>0.002124315</v>
       </c>
     </row>
     <row r="56">
@@ -1007,7 +1007,7 @@
         <v>15.9638</v>
       </c>
       <c r="B56" s="9" t="n">
-        <v>0.001835299</v>
+        <v>0.001787276</v>
       </c>
     </row>
     <row r="57">
@@ -1015,7 +1015,7 @@
         <v>16.3296</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>0.001562299</v>
+        <v>0.001530804</v>
       </c>
     </row>
     <row r="58">
@@ -1023,7 +1023,7 @@
         <v>16.6954</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>0.001347441</v>
+        <v>0.001304734</v>
       </c>
     </row>
     <row r="59">
@@ -1031,7 +1031,7 @@
         <v>17.0613</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>0.001115072</v>
+        <v>0.001101654</v>
       </c>
     </row>
     <row r="60">
@@ -1039,7 +1039,7 @@
         <v>17.4271</v>
       </c>
       <c r="B60" s="9" t="n">
-        <v>0.0009215959</v>
+        <v>0.0009418916</v>
       </c>
     </row>
     <row r="61">
@@ -1047,7 +1047,7 @@
         <v>17.7929</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>0.0007718397</v>
+        <v>0.0007896831</v>
       </c>
     </row>
     <row r="62">
@@ -1055,7 +1055,7 @@
         <v>18.1588</v>
       </c>
       <c r="B62" s="9" t="n">
-        <v>0.0006446410000000001</v>
+        <v>0.0006569315</v>
       </c>
     </row>
     <row r="63">
@@ -1063,7 +1063,7 @@
         <v>18.5246</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>0.0005571662</v>
+        <v>0.0005554956</v>
       </c>
     </row>
     <row r="64">
@@ -1071,7 +1071,7 @@
         <v>18.8904</v>
       </c>
       <c r="B64" s="9" t="n">
-        <v>0.0004496503</v>
+        <v>0.0004530894</v>
       </c>
     </row>
     <row r="65">
@@ -1079,7 +1079,7 @@
         <v>19.2563</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>0.0003703874</v>
+        <v>0.0003786737</v>
       </c>
     </row>
     <row r="66">
@@ -1087,7 +1087,7 @@
         <v>19.6221</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>0.0003146186</v>
+        <v>0.0003085618</v>
       </c>
     </row>
     <row r="67">
@@ -1095,7 +1095,7 @@
         <v>19.9879</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>0.0002557648</v>
+        <v>0.0002446449</v>
       </c>
     </row>
     <row r="68">
@@ -1103,7 +1103,7 @@
         <v>20.3538</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>0.0002065315</v>
+        <v>0.0002101598</v>
       </c>
     </row>
     <row r="69">
@@ -1111,7 +1111,7 @@
         <v>20.7196</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>0.0001731096</v>
+        <v>0.0001602708</v>
       </c>
     </row>
     <row r="70">
@@ -1119,7 +1119,7 @@
         <v>21.0854</v>
       </c>
       <c r="B70" s="9" t="n">
-        <v>0.0001346714</v>
+        <v>0.0001375224</v>
       </c>
     </row>
     <row r="71">
@@ -1127,7 +1127,7 @@
         <v>21.4513</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>0.0001041175</v>
+        <v>0.0001223888</v>
       </c>
     </row>
     <row r="72">
@@ -1135,7 +1135,7 @@
         <v>21.8171</v>
       </c>
       <c r="B72" s="9" t="n">
-        <v>8.901416e-05</v>
+        <v>8.816166e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>851105</t>
+          <t>790069</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
         <v>0.2329</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>0.1157213</v>
+        <v>0.1279314</v>
       </c>
     </row>
     <row r="14">
@@ -1295,7 +1295,7 @@
         <v>0.5988</v>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.1364491</v>
+        <v>0.1383799</v>
       </c>
     </row>
     <row r="15">
@@ -1303,7 +1303,7 @@
         <v>0.9646</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>0.1364127</v>
+        <v>0.1318458</v>
       </c>
     </row>
     <row r="16">
@@ -1311,7 +1311,7 @@
         <v>1.3304</v>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.1301215</v>
+        <v>0.1296057</v>
       </c>
     </row>
     <row r="17">
@@ -1319,7 +1319,7 @@
         <v>1.6963</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>0.1199853</v>
+        <v>0.121551</v>
       </c>
     </row>
     <row r="18">
@@ -1327,7 +1327,7 @@
         <v>2.0621</v>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.1092081</v>
+        <v>0.1136756</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>2.4279</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>0.09665857</v>
+        <v>0.09950185</v>
       </c>
     </row>
     <row r="20">
@@ -1343,7 +1343,7 @@
         <v>2.7938</v>
       </c>
       <c r="B20" s="9" t="n">
-        <v>0.08946527999999999</v>
+        <v>0.08929126</v>
       </c>
     </row>
     <row r="21">
@@ -1351,7 +1351,7 @@
         <v>3.1596</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>0.07790171</v>
+        <v>0.08041019000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1359,7 +1359,7 @@
         <v>3.5254</v>
       </c>
       <c r="B22" s="9" t="n">
-        <v>0.06792968000000001</v>
+        <v>0.07099112</v>
       </c>
     </row>
     <row r="23">
@@ -1367,7 +1367,7 @@
         <v>3.8912</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>0.05862615</v>
+        <v>0.06157983</v>
       </c>
     </row>
     <row r="24">
@@ -1375,7 +1375,7 @@
         <v>4.2571</v>
       </c>
       <c r="B24" s="9" t="n">
-        <v>0.05080312</v>
+        <v>0.05370494</v>
       </c>
     </row>
     <row r="25">
@@ -1383,7 +1383,7 @@
         <v>4.6229</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>0.0453317</v>
+        <v>0.04585523</v>
       </c>
     </row>
     <row r="26">
@@ -1391,7 +1391,7 @@
         <v>4.9887</v>
       </c>
       <c r="B26" s="9" t="n">
-        <v>0.03994984</v>
+        <v>0.04074065</v>
       </c>
     </row>
     <row r="27">
@@ -1399,7 +1399,7 @@
         <v>5.3546</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>0.034958</v>
+        <v>0.03626734</v>
       </c>
     </row>
     <row r="28">
@@ -1407,7 +1407,7 @@
         <v>5.7204</v>
       </c>
       <c r="B28" s="9" t="n">
-        <v>0.03192144</v>
+        <v>0.03152257</v>
       </c>
     </row>
     <row r="29">
@@ -1415,7 +1415,7 @@
         <v>6.0862</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>0.02798756</v>
+        <v>0.02802176</v>
       </c>
     </row>
     <row r="30">
@@ -1423,7 +1423,7 @@
         <v>6.4521</v>
       </c>
       <c r="B30" s="9" t="n">
-        <v>0.0259884</v>
+        <v>0.02526826</v>
       </c>
     </row>
     <row r="31">
@@ -1431,7 +1431,7 @@
         <v>6.8179</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>0.0237294</v>
+        <v>0.02293988</v>
       </c>
     </row>
     <row r="32">
@@ -1439,7 +1439,7 @@
         <v>7.1837</v>
       </c>
       <c r="B32" s="9" t="n">
-        <v>0.0218284</v>
+        <v>0.02010311</v>
       </c>
     </row>
     <row r="33">
@@ -1447,7 +1447,7 @@
         <v>7.5496</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>0.01985892</v>
+        <v>0.0180769</v>
       </c>
     </row>
     <row r="34">
@@ -1455,7 +1455,7 @@
         <v>7.9154</v>
       </c>
       <c r="B34" s="9" t="n">
-        <v>0.01745786</v>
+        <v>0.01665564</v>
       </c>
     </row>
     <row r="35">
@@ -1463,7 +1463,7 @@
         <v>8.2812</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>0.01602727</v>
+        <v>0.01543613</v>
       </c>
     </row>
     <row r="36">
@@ -1471,7 +1471,7 @@
         <v>8.6471</v>
       </c>
       <c r="B36" s="9" t="n">
-        <v>0.01383161</v>
+        <v>0.01349451</v>
       </c>
     </row>
     <row r="37">
@@ -1479,7 +1479,7 @@
         <v>9.0129</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>0.01284086</v>
+        <v>0.01198776</v>
       </c>
     </row>
     <row r="38">
@@ -1487,7 +1487,7 @@
         <v>9.3788</v>
       </c>
       <c r="B38" s="9" t="n">
-        <v>0.01168887</v>
+        <v>0.01093267</v>
       </c>
     </row>
     <row r="39">
@@ -1495,7 +1495,7 @@
         <v>9.7446</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>0.01056884</v>
+        <v>0.01002192</v>
       </c>
     </row>
     <row r="40">
@@ -1503,7 +1503,7 @@
         <v>10.1104</v>
       </c>
       <c r="B40" s="9" t="n">
-        <v>0.009731488999999999</v>
+        <v>0.008838809</v>
       </c>
     </row>
     <row r="41">
@@ -1511,7 +1511,7 @@
         <v>10.4763</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.008020717</v>
+        <v>0.008199348</v>
       </c>
     </row>
     <row r="42">
@@ -1519,7 +1519,7 @@
         <v>10.8421</v>
       </c>
       <c r="B42" s="9" t="n">
-        <v>0.007587273</v>
+        <v>0.007347586</v>
       </c>
     </row>
     <row r="43">
@@ -1527,7 +1527,7 @@
         <v>11.2079</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>0.006940712</v>
+        <v>0.006536499</v>
       </c>
     </row>
     <row r="44">
@@ -1535,7 +1535,7 @@
         <v>11.5738</v>
       </c>
       <c r="B44" s="9" t="n">
-        <v>0.006170193</v>
+        <v>0.005833626</v>
       </c>
     </row>
     <row r="45">
@@ -1543,7 +1543,7 @@
         <v>11.9396</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>0.005344188</v>
+        <v>0.005149051</v>
       </c>
     </row>
     <row r="46">
@@ -1551,7 +1551,7 @@
         <v>12.3054</v>
       </c>
       <c r="B46" s="9" t="n">
-        <v>0.004793759</v>
+        <v>0.004717413</v>
       </c>
     </row>
     <row r="47">
@@ -1559,7 +1559,7 @@
         <v>12.6713</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>0.004208996</v>
+        <v>0.004187535</v>
       </c>
     </row>
     <row r="48">
@@ -1567,7 +1567,7 @@
         <v>13.0371</v>
       </c>
       <c r="B48" s="9" t="n">
-        <v>0.003973136</v>
+        <v>0.003769542</v>
       </c>
     </row>
     <row r="49">
@@ -1575,7 +1575,7 @@
         <v>13.4029</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>0.003536348</v>
+        <v>0.003346819</v>
       </c>
     </row>
     <row r="50">
@@ -1583,7 +1583,7 @@
         <v>13.7688</v>
       </c>
       <c r="B50" s="9" t="n">
-        <v>0.002926469</v>
+        <v>0.002840871</v>
       </c>
     </row>
     <row r="51">
@@ -1591,7 +1591,7 @@
         <v>14.1346</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>0.002614572</v>
+        <v>0.002425164</v>
       </c>
     </row>
     <row r="52">
@@ -1599,7 +1599,7 @@
         <v>14.5004</v>
       </c>
       <c r="B52" s="9" t="n">
-        <v>0.002311078</v>
+        <v>0.002115093</v>
       </c>
     </row>
     <row r="53">
@@ -1607,7 +1607,7 @@
         <v>14.8663</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>0.002088088</v>
+        <v>0.001890348</v>
       </c>
     </row>
     <row r="54">
@@ -1615,7 +1615,7 @@
         <v>15.2321</v>
       </c>
       <c r="B54" s="9" t="n">
-        <v>0.001945007</v>
+        <v>0.001776087</v>
       </c>
     </row>
     <row r="55">
@@ -1623,7 +1623,7 @@
         <v>15.5979</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>0.001549866</v>
+        <v>0.001560413</v>
       </c>
     </row>
     <row r="56">
@@ -1631,7 +1631,7 @@
         <v>15.9638</v>
       </c>
       <c r="B56" s="9" t="n">
-        <v>0.001393537</v>
+        <v>0.001226834</v>
       </c>
     </row>
     <row r="57">
@@ -1639,7 +1639,7 @@
         <v>16.3296</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>0.001166108</v>
+        <v>0.001012416</v>
       </c>
     </row>
     <row r="58">
@@ -1647,7 +1647,7 @@
         <v>16.6954</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>0.0009619696</v>
+        <v>0.0008681567</v>
       </c>
     </row>
     <row r="59">
@@ -1655,7 +1655,7 @@
         <v>17.0613</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>0.000929796</v>
+        <v>0.0006449376</v>
       </c>
     </row>
     <row r="60">
@@ -1663,7 +1663,7 @@
         <v>17.4271</v>
       </c>
       <c r="B60" s="9" t="n">
-        <v>0.0007335223</v>
+        <v>0.0006007903999999999</v>
       </c>
     </row>
     <row r="61">
@@ -1671,7 +1671,7 @@
         <v>17.7929</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>0.00059936</v>
+        <v>0.0005050662</v>
       </c>
     </row>
     <row r="62">
@@ -1679,7 +1679,7 @@
         <v>18.1588</v>
       </c>
       <c r="B62" s="9" t="n">
-        <v>0.0004838423</v>
+        <v>0.000448738</v>
       </c>
     </row>
     <row r="63">
@@ -1687,7 +1687,7 @@
         <v>18.5246</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>0.0004237382</v>
+        <v>0.0003758715</v>
       </c>
     </row>
     <row r="64">
@@ -1695,7 +1695,7 @@
         <v>18.8904</v>
       </c>
       <c r="B64" s="9" t="n">
-        <v>0.0003485691</v>
+        <v>0.0003140308</v>
       </c>
     </row>
     <row r="65">
@@ -1703,7 +1703,7 @@
         <v>19.2563</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>0.0003261842</v>
+        <v>0.000263668</v>
       </c>
     </row>
     <row r="66">
@@ -1711,7 +1711,7 @@
         <v>19.6221</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>0.0002759306</v>
+        <v>0.000222879</v>
       </c>
     </row>
     <row r="67">
@@ -1719,7 +1719,7 @@
         <v>19.9879</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>0.0002395793</v>
+        <v>0.0001929356</v>
       </c>
     </row>
     <row r="68">
@@ -1727,7 +1727,7 @@
         <v>20.3538</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>0.0001917868</v>
+        <v>0.0001435873</v>
       </c>
     </row>
     <row r="69">
@@ -1735,7 +1735,7 @@
         <v>20.7196</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>0.0001695936</v>
+        <v>0.0001232881</v>
       </c>
     </row>
     <row r="70">
@@ -1743,7 +1743,7 @@
         <v>21.0854</v>
       </c>
       <c r="B70" s="9" t="n">
-        <v>0.0001442995</v>
+        <v>0.0001025993</v>
       </c>
     </row>
     <row r="71">
@@ -1751,7 +1751,7 @@
         <v>21.4513</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>0.0001215348</v>
+        <v>7.778643000000001e-05</v>
       </c>
     </row>
     <row r="72">
@@ -1759,7 +1759,7 @@
         <v>21.8171</v>
       </c>
       <c r="B72" s="9" t="n">
-        <v>9.296601e-05</v>
+        <v>8.603129e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>55919</t>
+          <t>49945</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
         <v>0.2329</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>0.182589</v>
+        <v>0.1172462</v>
       </c>
     </row>
     <row r="14">
@@ -1919,7 +1919,7 @@
         <v>0.5988</v>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.2243441</v>
+        <v>0.1661457</v>
       </c>
     </row>
     <row r="15">
@@ -1927,7 +1927,7 @@
         <v>0.9646</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>0.1913165</v>
+        <v>0.1674882</v>
       </c>
     </row>
     <row r="16">
@@ -1935,7 +1935,7 @@
         <v>1.3304</v>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.1813758</v>
+        <v>0.1726272</v>
       </c>
     </row>
     <row r="17">
@@ -1943,7 +1943,7 @@
         <v>1.6963</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>0.1448722</v>
+        <v>0.1541865</v>
       </c>
     </row>
     <row r="18">
@@ -1951,7 +1951,7 @@
         <v>2.0621</v>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.1306781</v>
+        <v>0.1333955</v>
       </c>
     </row>
     <row r="19">
@@ -1959,7 +1959,7 @@
         <v>2.4279</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>0.1183564</v>
+        <v>0.1344311</v>
       </c>
     </row>
     <row r="20">
@@ -1967,7 +1967,7 @@
         <v>2.7938</v>
       </c>
       <c r="B20" s="9" t="n">
-        <v>0.100518</v>
+        <v>0.09723498</v>
       </c>
     </row>
     <row r="21">
@@ -1975,7 +1975,7 @@
         <v>3.1596</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>0.08685902</v>
+        <v>0.08345118999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1983,7 +1983,7 @@
         <v>3.5254</v>
       </c>
       <c r="B22" s="9" t="n">
-        <v>0.0781853</v>
+        <v>0.06879191</v>
       </c>
     </row>
     <row r="23">
@@ -1991,7 +1991,7 @@
         <v>3.8912</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>0.06590221</v>
+        <v>0.06361790000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1999,7 +1999,7 @@
         <v>4.2571</v>
       </c>
       <c r="B24" s="9" t="n">
-        <v>0.05066196</v>
+        <v>0.04786724</v>
       </c>
     </row>
     <row r="25">
@@ -2007,7 +2007,7 @@
         <v>4.6229</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>0.0431257</v>
+        <v>0.0424949</v>
       </c>
     </row>
     <row r="26">
@@ -2015,7 +2015,7 @@
         <v>4.9887</v>
       </c>
       <c r="B26" s="9" t="n">
-        <v>0.03607561</v>
+        <v>0.03737557</v>
       </c>
     </row>
     <row r="27">
@@ -2023,7 +2023,7 @@
         <v>5.3546</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>0.03043965</v>
+        <v>0.02961374</v>
       </c>
     </row>
     <row r="28">
@@ -2031,7 +2031,7 @@
         <v>5.7204</v>
       </c>
       <c r="B28" s="9" t="n">
-        <v>0.02586623</v>
+        <v>0.02558221</v>
       </c>
     </row>
     <row r="29">
@@ -2039,7 +2039,7 @@
         <v>6.0862</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>0.01977553</v>
+        <v>0.02506789</v>
       </c>
     </row>
     <row r="30">
@@ -2047,7 +2047,7 @@
         <v>6.4521</v>
       </c>
       <c r="B30" s="9" t="n">
-        <v>0.01662267</v>
+        <v>0.02385085</v>
       </c>
     </row>
     <row r="31">
@@ -2055,7 +2055,7 @@
         <v>6.8179</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>0.01641443</v>
+        <v>0.02133506</v>
       </c>
     </row>
     <row r="32">
@@ -2063,7 +2063,7 @@
         <v>7.1837</v>
       </c>
       <c r="B32" s="9" t="n">
-        <v>0.01301212</v>
+        <v>0.0175965</v>
       </c>
     </row>
     <row r="33">
@@ -2071,7 +2071,7 @@
         <v>7.5496</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>0.0122116</v>
+        <v>0.01451338</v>
       </c>
     </row>
     <row r="34">
@@ -2079,7 +2079,7 @@
         <v>7.9154</v>
       </c>
       <c r="B34" s="9" t="n">
-        <v>0.01143858</v>
+        <v>0.01265538</v>
       </c>
     </row>
     <row r="35">
@@ -2087,7 +2087,7 @@
         <v>8.2812</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>0.009583057000000001</v>
+        <v>0.01096411</v>
       </c>
     </row>
     <row r="36">
@@ -2095,7 +2095,7 @@
         <v>8.6471</v>
       </c>
       <c r="B36" s="9" t="n">
-        <v>0.008628564999999999</v>
+        <v>0.009611998</v>
       </c>
     </row>
     <row r="37">
@@ -2103,7 +2103,7 @@
         <v>9.0129</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>0.007684787</v>
+        <v>0.009396656</v>
       </c>
     </row>
     <row r="38">
@@ -2111,7 +2111,7 @@
         <v>9.3788</v>
       </c>
       <c r="B38" s="9" t="n">
-        <v>0.008125215</v>
+        <v>0.007780644</v>
       </c>
     </row>
     <row r="39">
@@ -2119,7 +2119,7 @@
         <v>9.7446</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>0.005915662</v>
+        <v>0.006931293</v>
       </c>
     </row>
     <row r="40">
@@ -2127,7 +2127,7 @@
         <v>10.1104</v>
       </c>
       <c r="B40" s="9" t="n">
-        <v>0.00411311</v>
+        <v>0.007235417</v>
       </c>
     </row>
     <row r="41">
@@ -2135,7 +2135,7 @@
         <v>10.4763</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.003677452</v>
+        <v>0.005381743</v>
       </c>
     </row>
     <row r="42">
@@ -2143,7 +2143,7 @@
         <v>10.8421</v>
       </c>
       <c r="B42" s="9" t="n">
-        <v>0.00307934</v>
+        <v>0.005523069</v>
       </c>
     </row>
     <row r="43">
@@ -2151,7 +2151,7 @@
         <v>11.2079</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>0.00365781</v>
+        <v>0.004728617</v>
       </c>
     </row>
     <row r="44">
@@ -2159,7 +2159,7 @@
         <v>11.5738</v>
       </c>
       <c r="B44" s="9" t="n">
-        <v>0.002980416</v>
+        <v>0.003783812</v>
       </c>
     </row>
     <row r="45">
@@ -2167,7 +2167,7 @@
         <v>11.9396</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>0.003274621</v>
+        <v>0.003107136</v>
       </c>
     </row>
     <row r="46">
@@ -2175,7 +2175,7 @@
         <v>12.3054</v>
       </c>
       <c r="B46" s="9" t="n">
-        <v>0.002667036</v>
+        <v>0.002514065</v>
       </c>
     </row>
     <row r="47">
@@ -2183,7 +2183,7 @@
         <v>12.6713</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>0.002986026</v>
+        <v>0.002616001</v>
       </c>
     </row>
     <row r="48">
@@ -2191,7 +2191,7 @@
         <v>13.0371</v>
       </c>
       <c r="B48" s="9" t="n">
-        <v>0.002292662</v>
+        <v>0.001790155</v>
       </c>
     </row>
     <row r="49">
@@ -2199,7 +2199,7 @@
         <v>13.4029</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>0.001806249</v>
+        <v>0.001960065</v>
       </c>
     </row>
     <row r="50">
@@ -2207,7 +2207,7 @@
         <v>13.7688</v>
       </c>
       <c r="B50" s="9" t="n">
-        <v>0.001438874</v>
+        <v>0.001461459</v>
       </c>
     </row>
     <row r="51">
@@ -2215,7 +2215,7 @@
         <v>14.1346</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>0.001719792</v>
+        <v>0.001151024</v>
       </c>
     </row>
     <row r="52">
@@ -2223,7 +2223,7 @@
         <v>14.5004</v>
       </c>
       <c r="B52" s="9" t="n">
-        <v>0.001466419</v>
+        <v>0.001093257</v>
       </c>
     </row>
     <row r="53">
@@ -2231,7 +2231,7 @@
         <v>14.8663</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>0.001524488</v>
+        <v>0.001406479</v>
       </c>
     </row>
     <row r="54">
@@ -2239,7 +2239,7 @@
         <v>15.2321</v>
       </c>
       <c r="B54" s="9" t="n">
-        <v>0.001029148</v>
+        <v>0.0009684299</v>
       </c>
     </row>
     <row r="55">
@@ -2247,7 +2247,7 @@
         <v>15.5979</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>0.0005085038</v>
+        <v>0.001026354</v>
       </c>
     </row>
     <row r="56">
@@ -2255,7 +2255,7 @@
         <v>15.9638</v>
       </c>
       <c r="B56" s="9" t="n">
-        <v>0.0005516818</v>
+        <v>0.0007403295</v>
       </c>
     </row>
     <row r="57">
@@ -2263,7 +2263,7 @@
         <v>16.3296</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>0.0007757755</v>
+        <v>0.0009759863</v>
       </c>
     </row>
     <row r="58">
@@ -2271,7 +2271,7 @@
         <v>16.6954</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>0.0007792169</v>
+        <v>0.0006703014</v>
       </c>
     </row>
     <row r="59">
@@ -2279,7 +2279,7 @@
         <v>17.0613</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>0.0003320444</v>
+        <v>0.0005171993</v>
       </c>
     </row>
     <row r="60">
@@ -2287,7 +2287,7 @@
         <v>17.4271</v>
       </c>
       <c r="B60" s="9" t="n">
-        <v>0.0002229384</v>
+        <v>0.0004854988</v>
       </c>
     </row>
     <row r="61">
@@ -2295,7 +2295,7 @@
         <v>17.7929</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>0.0002438593</v>
+        <v>0.0004155518</v>
       </c>
     </row>
     <row r="62">
@@ -2303,7 +2303,7 @@
         <v>18.1588</v>
       </c>
       <c r="B62" s="9" t="n">
-        <v>0.000206906</v>
+        <v>0.0002442358</v>
       </c>
     </row>
     <row r="63">
@@ -2311,7 +2311,7 @@
         <v>18.5246</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>0.0001934721</v>
+        <v>0.0002545391</v>
       </c>
     </row>
     <row r="64">
@@ -2319,7 +2319,7 @@
         <v>18.8904</v>
       </c>
       <c r="B64" s="9" t="n">
-        <v>0.0001352397</v>
+        <v>0.0001386343</v>
       </c>
     </row>
     <row r="65">
@@ -2327,7 +2327,7 @@
         <v>19.2563</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>0.0001004616</v>
+        <v>0.0001622767</v>
       </c>
     </row>
     <row r="66">
@@ -2335,7 +2335,7 @@
         <v>19.6221</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>8.846287e-05</v>
+        <v>0.0001854887</v>
       </c>
     </row>
     <row r="67">
@@ -2343,7 +2343,7 @@
         <v>19.9879</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>6.573718e-05</v>
+        <v>0.0001837834</v>
       </c>
     </row>
     <row r="68">
@@ -2351,7 +2351,7 @@
         <v>20.3538</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>0.0001085729</v>
+        <v>0.0001335578</v>
       </c>
     </row>
     <row r="69">
@@ -2359,7 +2359,7 @@
         <v>20.7196</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>0.0001721762</v>
+        <v>0.0001444074</v>
       </c>
     </row>
     <row r="70">
@@ -2367,7 +2367,7 @@
         <v>21.0854</v>
       </c>
       <c r="B70" s="9" t="n">
-        <v>9.600526e-05</v>
+        <v>8.35037e-05</v>
       </c>
     </row>
     <row r="71">
@@ -2375,7 +2375,7 @@
         <v>21.4513</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>0.0001163349</v>
+        <v>4.730777e-05</v>
       </c>
     </row>
     <row r="72">
@@ -2383,7 +2383,7 @@
         <v>21.8171</v>
       </c>
       <c r="B72" s="9" t="n">
-        <v>4.194742e-05</v>
+        <v>5.863682e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2456,19 +2456,19 @@
         <v>0.2329</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>0.1151691</v>
+        <v>0.1193456</v>
       </c>
       <c r="C3" s="8" t="n">
         <v>0.2329</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.1157213</v>
+        <v>0.1279314</v>
       </c>
       <c r="E3" s="8" t="n">
         <v>0.2329</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>0.182589</v>
+        <v>0.1172462</v>
       </c>
     </row>
     <row r="4">
@@ -2476,19 +2476,19 @@
         <v>0.5988</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>0.1096888</v>
+        <v>0.1140152</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>0.5988</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>0.1364491</v>
+        <v>0.1383799</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>0.5988</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>0.2243441</v>
+        <v>0.1661457</v>
       </c>
     </row>
     <row r="5">
@@ -2496,19 +2496,19 @@
         <v>0.9646</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.1011442</v>
+        <v>0.1026151</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>0.9646</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.1364127</v>
+        <v>0.1318458</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>0.9646</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>0.1913165</v>
+        <v>0.1674882</v>
       </c>
     </row>
     <row r="6">
@@ -2516,19 +2516,19 @@
         <v>1.3304</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>0.09280173999999999</v>
+        <v>0.09476811</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>1.3304</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>0.1301215</v>
+        <v>0.1296057</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>1.3304</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>0.1813758</v>
+        <v>0.1726272</v>
       </c>
     </row>
     <row r="7">
@@ -2536,19 +2536,19 @@
         <v>1.6963</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>0.08491606</v>
+        <v>0.08721385</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>1.6963</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.1199853</v>
+        <v>0.121551</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>1.6963</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>0.1448722</v>
+        <v>0.1541865</v>
       </c>
     </row>
     <row r="8">
@@ -2556,19 +2556,19 @@
         <v>2.0621</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>0.07945355</v>
+        <v>0.07952244999999999</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>2.0621</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0.1092081</v>
+        <v>0.1136756</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2.0621</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>0.1306781</v>
+        <v>0.1333955</v>
       </c>
     </row>
     <row r="9">
@@ -2576,19 +2576,19 @@
         <v>2.4279</v>
       </c>
       <c r="B9" s="9" t="n">
-        <v>0.07291735000000001</v>
+        <v>0.07321133000000001</v>
       </c>
       <c r="C9" s="8" t="n">
         <v>2.4279</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.09665857</v>
+        <v>0.09950185</v>
       </c>
       <c r="E9" s="8" t="n">
         <v>2.4279</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>0.1183564</v>
+        <v>0.1344311</v>
       </c>
     </row>
     <row r="10">
@@ -2596,19 +2596,19 @@
         <v>2.7938</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.0680255</v>
+        <v>0.06774012</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>2.7938</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0.08946527999999999</v>
+        <v>0.08929126</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>2.7938</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>0.100518</v>
+        <v>0.09723498</v>
       </c>
     </row>
     <row r="11">
@@ -2616,19 +2616,19 @@
         <v>3.1596</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>0.06266961</v>
+        <v>0.06243023</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>3.1596</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.07790171</v>
+        <v>0.08041019000000001</v>
       </c>
       <c r="E11" s="8" t="n">
         <v>3.1596</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>0.08685902</v>
+        <v>0.08345118999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2636,19 +2636,19 @@
         <v>3.5254</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>0.05832175</v>
+        <v>0.05794753</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>3.5254</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.06792968000000001</v>
+        <v>0.07099112</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>3.5254</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>0.0781853</v>
+        <v>0.06879191</v>
       </c>
     </row>
     <row r="13">
@@ -2656,19 +2656,19 @@
         <v>3.8912</v>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.05396241</v>
+        <v>0.05377977</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>3.8912</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.05862615</v>
+        <v>0.06157983</v>
       </c>
       <c r="E13" s="8" t="n">
         <v>3.8912</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>0.06590221</v>
+        <v>0.06361790000000001</v>
       </c>
     </row>
     <row r="14">
@@ -2676,19 +2676,19 @@
         <v>4.2571</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>0.04925609</v>
+        <v>0.04907032</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>4.2571</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.05080312</v>
+        <v>0.05370494</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>4.2571</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0.05066196</v>
+        <v>0.04786724</v>
       </c>
     </row>
     <row r="15">
@@ -2696,19 +2696,19 @@
         <v>4.6229</v>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.04580698</v>
+        <v>0.04528294</v>
       </c>
       <c r="C15" s="8" t="n">
         <v>4.6229</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.0453317</v>
+        <v>0.04585523</v>
       </c>
       <c r="E15" s="8" t="n">
         <v>4.6229</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>0.0431257</v>
+        <v>0.0424949</v>
       </c>
     </row>
     <row r="16">
@@ -2716,19 +2716,19 @@
         <v>4.9887</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>0.04251213</v>
+        <v>0.04256852</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>4.9887</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.03994984</v>
+        <v>0.04074065</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>4.9887</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>0.03607561</v>
+        <v>0.03737557</v>
       </c>
     </row>
     <row r="17">
@@ -2736,19 +2736,19 @@
         <v>5.3546</v>
       </c>
       <c r="B17" s="9" t="n">
-        <v>0.03934945</v>
+        <v>0.03943648</v>
       </c>
       <c r="C17" s="8" t="n">
         <v>5.3546</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.034958</v>
+        <v>0.03626734</v>
       </c>
       <c r="E17" s="8" t="n">
         <v>5.3546</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>0.03043965</v>
+        <v>0.02961374</v>
       </c>
     </row>
     <row r="18">
@@ -2756,19 +2756,19 @@
         <v>5.7204</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>0.03688484</v>
+        <v>0.03637444</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>5.7204</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.03192144</v>
+        <v>0.03152257</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>5.7204</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>0.02586623</v>
+        <v>0.02558221</v>
       </c>
     </row>
     <row r="19">
@@ -2776,19 +2776,19 @@
         <v>6.0862</v>
       </c>
       <c r="B19" s="9" t="n">
-        <v>0.03401831</v>
+        <v>0.03374614</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>6.0862</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.02798756</v>
+        <v>0.02802176</v>
       </c>
       <c r="E19" s="8" t="n">
         <v>6.0862</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>0.01977553</v>
+        <v>0.02506789</v>
       </c>
     </row>
     <row r="20">
@@ -2796,19 +2796,19 @@
         <v>6.4521</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>0.03152634</v>
+        <v>0.03112772</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>6.4521</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.0259884</v>
+        <v>0.02526826</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>6.4521</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.01662267</v>
+        <v>0.02385085</v>
       </c>
     </row>
     <row r="21">
@@ -2816,19 +2816,19 @@
         <v>6.8179</v>
       </c>
       <c r="B21" s="9" t="n">
-        <v>0.02902703</v>
+        <v>0.02879163</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>6.8179</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.0237294</v>
+        <v>0.02293988</v>
       </c>
       <c r="E21" s="8" t="n">
         <v>6.8179</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>0.01641443</v>
+        <v>0.02133506</v>
       </c>
     </row>
     <row r="22">
@@ -2836,19 +2836,19 @@
         <v>7.1837</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>0.02693607</v>
+        <v>0.02686982</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>7.1837</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.0218284</v>
+        <v>0.02010311</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>7.1837</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.01301212</v>
+        <v>0.0175965</v>
       </c>
     </row>
     <row r="23">
@@ -2856,19 +2856,19 @@
         <v>7.5496</v>
       </c>
       <c r="B23" s="9" t="n">
-        <v>0.0248232</v>
+        <v>0.02487285</v>
       </c>
       <c r="C23" s="8" t="n">
         <v>7.5496</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.01985892</v>
+        <v>0.0180769</v>
       </c>
       <c r="E23" s="8" t="n">
         <v>7.5496</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>0.0122116</v>
+        <v>0.01451338</v>
       </c>
     </row>
     <row r="24">
@@ -2876,19 +2876,19 @@
         <v>7.9154</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>0.02311112</v>
+        <v>0.0230132</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>7.9154</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.01745786</v>
+        <v>0.01665564</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>7.9154</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.01143858</v>
+        <v>0.01265538</v>
       </c>
     </row>
     <row r="25">
@@ -2896,19 +2896,19 @@
         <v>8.2812</v>
       </c>
       <c r="B25" s="9" t="n">
-        <v>0.02122426</v>
+        <v>0.02109745</v>
       </c>
       <c r="C25" s="8" t="n">
         <v>8.2812</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.01602727</v>
+        <v>0.01543613</v>
       </c>
       <c r="E25" s="8" t="n">
         <v>8.2812</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>0.009583057000000001</v>
+        <v>0.01096411</v>
       </c>
     </row>
     <row r="26">
@@ -2916,19 +2916,19 @@
         <v>8.6471</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>0.01948866</v>
+        <v>0.01935205</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>8.6471</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>0.01383161</v>
+        <v>0.01349451</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>8.6471</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>0.008628564999999999</v>
+        <v>0.009611998</v>
       </c>
     </row>
     <row r="27">
@@ -2936,19 +2936,19 @@
         <v>9.0129</v>
       </c>
       <c r="B27" s="9" t="n">
-        <v>0.01800795</v>
+        <v>0.01805519</v>
       </c>
       <c r="C27" s="8" t="n">
         <v>9.0129</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.01284086</v>
+        <v>0.01198776</v>
       </c>
       <c r="E27" s="8" t="n">
         <v>9.0129</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>0.007684787</v>
+        <v>0.009396656</v>
       </c>
     </row>
     <row r="28">
@@ -2956,19 +2956,19 @@
         <v>9.3788</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>0.01652575</v>
+        <v>0.01650989</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>9.3788</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>0.01168887</v>
+        <v>0.01093267</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>9.3788</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>0.008125215</v>
+        <v>0.007780644</v>
       </c>
     </row>
     <row r="29">
@@ -2976,19 +2976,19 @@
         <v>9.7446</v>
       </c>
       <c r="B29" s="9" t="n">
-        <v>0.01515833</v>
+        <v>0.0149138</v>
       </c>
       <c r="C29" s="8" t="n">
         <v>9.7446</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.01056884</v>
+        <v>0.01002192</v>
       </c>
       <c r="E29" s="8" t="n">
         <v>9.7446</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>0.005915662</v>
+        <v>0.006931293</v>
       </c>
     </row>
     <row r="30">
@@ -2996,19 +2996,19 @@
         <v>10.1104</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>0.01386963</v>
+        <v>0.01355793</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>10.1104</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>0.009731488999999999</v>
+        <v>0.008838809</v>
       </c>
       <c r="E30" s="6" t="n">
         <v>10.1104</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>0.00411311</v>
+        <v>0.007235417</v>
       </c>
     </row>
     <row r="31">
@@ -3016,19 +3016,19 @@
         <v>10.4763</v>
       </c>
       <c r="B31" s="9" t="n">
-        <v>0.01251173</v>
+        <v>0.0124706</v>
       </c>
       <c r="C31" s="8" t="n">
         <v>10.4763</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.008020717</v>
+        <v>0.008199348</v>
       </c>
       <c r="E31" s="8" t="n">
         <v>10.4763</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>0.003677452</v>
+        <v>0.005381743</v>
       </c>
     </row>
     <row r="32">
@@ -3036,19 +3036,19 @@
         <v>10.8421</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>0.01139333</v>
+        <v>0.01136191</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>10.8421</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>0.007587273</v>
+        <v>0.007347586</v>
       </c>
       <c r="E32" s="6" t="n">
         <v>10.8421</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>0.00307934</v>
+        <v>0.005523069</v>
       </c>
     </row>
     <row r="33">
@@ -3056,19 +3056,19 @@
         <v>11.2079</v>
       </c>
       <c r="B33" s="9" t="n">
-        <v>0.01030612</v>
+        <v>0.01017649</v>
       </c>
       <c r="C33" s="8" t="n">
         <v>11.2079</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.006940712</v>
+        <v>0.006536499</v>
       </c>
       <c r="E33" s="8" t="n">
         <v>11.2079</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>0.00365781</v>
+        <v>0.004728617</v>
       </c>
     </row>
     <row r="34">
@@ -3076,19 +3076,19 @@
         <v>11.5738</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>0.009308637999999999</v>
+        <v>0.009110596</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>11.5738</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>0.006170193</v>
+        <v>0.005833626</v>
       </c>
       <c r="E34" s="6" t="n">
         <v>11.5738</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>0.002980416</v>
+        <v>0.003783812</v>
       </c>
     </row>
     <row r="35">
@@ -3096,19 +3096,19 @@
         <v>11.9396</v>
       </c>
       <c r="B35" s="9" t="n">
-        <v>0.008203039000000001</v>
+        <v>0.008042179999999999</v>
       </c>
       <c r="C35" s="8" t="n">
         <v>11.9396</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.005344188</v>
+        <v>0.005149051</v>
       </c>
       <c r="E35" s="8" t="n">
         <v>11.9396</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>0.003274621</v>
+        <v>0.003107136</v>
       </c>
     </row>
     <row r="36">
@@ -3116,19 +3116,19 @@
         <v>12.3054</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>0.007301025</v>
+        <v>0.007092552</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>12.3054</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>0.004793759</v>
+        <v>0.004717413</v>
       </c>
       <c r="E36" s="6" t="n">
         <v>12.3054</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>0.002667036</v>
+        <v>0.002514065</v>
       </c>
     </row>
     <row r="37">
@@ -3136,19 +3136,19 @@
         <v>12.6713</v>
       </c>
       <c r="B37" s="9" t="n">
-        <v>0.006344912</v>
+        <v>0.006329598</v>
       </c>
       <c r="C37" s="8" t="n">
         <v>12.6713</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.004208996</v>
+        <v>0.004187535</v>
       </c>
       <c r="E37" s="8" t="n">
         <v>12.6713</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>0.002986026</v>
+        <v>0.002616001</v>
       </c>
     </row>
     <row r="38">
@@ -3156,19 +3156,19 @@
         <v>13.0371</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>0.005440954</v>
+        <v>0.005487783</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>13.0371</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>0.003973136</v>
+        <v>0.003769542</v>
       </c>
       <c r="E38" s="6" t="n">
         <v>13.0371</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>0.002292662</v>
+        <v>0.001790155</v>
       </c>
     </row>
     <row r="39">
@@ -3176,19 +3176,19 @@
         <v>13.4029</v>
       </c>
       <c r="B39" s="9" t="n">
-        <v>0.004815799</v>
+        <v>0.00480424</v>
       </c>
       <c r="C39" s="8" t="n">
         <v>13.4029</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.003536348</v>
+        <v>0.003346819</v>
       </c>
       <c r="E39" s="8" t="n">
         <v>13.4029</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>0.001806249</v>
+        <v>0.001960065</v>
       </c>
     </row>
     <row r="40">
@@ -3196,19 +3196,19 @@
         <v>13.7688</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>0.004098078</v>
+        <v>0.004153494</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>13.7688</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>0.002926469</v>
+        <v>0.002840871</v>
       </c>
       <c r="E40" s="6" t="n">
         <v>13.7688</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>0.001438874</v>
+        <v>0.001461459</v>
       </c>
     </row>
     <row r="41">
@@ -3216,19 +3216,19 @@
         <v>14.1346</v>
       </c>
       <c r="B41" s="9" t="n">
-        <v>0.003649953</v>
+        <v>0.003554152</v>
       </c>
       <c r="C41" s="8" t="n">
         <v>14.1346</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.002614572</v>
+        <v>0.002425164</v>
       </c>
       <c r="E41" s="8" t="n">
         <v>14.1346</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>0.001719792</v>
+        <v>0.001151024</v>
       </c>
     </row>
     <row r="42">
@@ -3236,19 +3236,19 @@
         <v>14.5004</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>0.003238296</v>
+        <v>0.003176313</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>14.5004</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>0.002311078</v>
+        <v>0.002115093</v>
       </c>
       <c r="E42" s="6" t="n">
         <v>14.5004</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>0.001466419</v>
+        <v>0.001093257</v>
       </c>
     </row>
     <row r="43">
@@ -3256,19 +3256,19 @@
         <v>14.8663</v>
       </c>
       <c r="B43" s="9" t="n">
-        <v>0.002829778</v>
+        <v>0.002784939</v>
       </c>
       <c r="C43" s="8" t="n">
         <v>14.8663</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.002088088</v>
+        <v>0.001890348</v>
       </c>
       <c r="E43" s="8" t="n">
         <v>14.8663</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>0.001524488</v>
+        <v>0.001406479</v>
       </c>
     </row>
     <row r="44">
@@ -3276,19 +3276,19 @@
         <v>15.2321</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>0.002411704</v>
+        <v>0.002448064</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>15.2321</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>0.001945007</v>
+        <v>0.001776087</v>
       </c>
       <c r="E44" s="6" t="n">
         <v>15.2321</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>0.001029148</v>
+        <v>0.0009684299</v>
       </c>
     </row>
     <row r="45">
@@ -3296,19 +3296,19 @@
         <v>15.5979</v>
       </c>
       <c r="B45" s="9" t="n">
-        <v>0.00210292</v>
+        <v>0.002124315</v>
       </c>
       <c r="C45" s="8" t="n">
         <v>15.5979</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.001549866</v>
+        <v>0.001560413</v>
       </c>
       <c r="E45" s="8" t="n">
         <v>15.5979</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>0.0005085038</v>
+        <v>0.001026354</v>
       </c>
     </row>
     <row r="46">
@@ -3316,19 +3316,19 @@
         <v>15.9638</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>0.001835299</v>
+        <v>0.001787276</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>15.9638</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>0.001393537</v>
+        <v>0.001226834</v>
       </c>
       <c r="E46" s="6" t="n">
         <v>15.9638</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>0.0005516818</v>
+        <v>0.0007403295</v>
       </c>
     </row>
     <row r="47">
@@ -3336,19 +3336,19 @@
         <v>16.3296</v>
       </c>
       <c r="B47" s="9" t="n">
-        <v>0.001562299</v>
+        <v>0.001530804</v>
       </c>
       <c r="C47" s="8" t="n">
         <v>16.3296</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.001166108</v>
+        <v>0.001012416</v>
       </c>
       <c r="E47" s="8" t="n">
         <v>16.3296</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>0.0007757755</v>
+        <v>0.0009759863</v>
       </c>
     </row>
     <row r="48">
@@ -3356,19 +3356,19 @@
         <v>16.6954</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>0.001347441</v>
+        <v>0.001304734</v>
       </c>
       <c r="C48" s="6" t="n">
         <v>16.6954</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>0.0009619696</v>
+        <v>0.0008681567</v>
       </c>
       <c r="E48" s="6" t="n">
         <v>16.6954</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>0.0007792169</v>
+        <v>0.0006703014</v>
       </c>
     </row>
     <row r="49">
@@ -3376,19 +3376,19 @@
         <v>17.0613</v>
       </c>
       <c r="B49" s="9" t="n">
-        <v>0.001115072</v>
+        <v>0.001101654</v>
       </c>
       <c r="C49" s="8" t="n">
         <v>17.0613</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.000929796</v>
+        <v>0.0006449376</v>
       </c>
       <c r="E49" s="8" t="n">
         <v>17.0613</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>0.0003320444</v>
+        <v>0.0005171993</v>
       </c>
     </row>
     <row r="50">
@@ -3396,19 +3396,19 @@
         <v>17.4271</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>0.0009215959</v>
+        <v>0.0009418916</v>
       </c>
       <c r="C50" s="6" t="n">
         <v>17.4271</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>0.0007335223</v>
+        <v>0.0006007903999999999</v>
       </c>
       <c r="E50" s="6" t="n">
         <v>17.4271</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>0.0002229384</v>
+        <v>0.0004854988</v>
       </c>
     </row>
     <row r="51">
@@ -3416,19 +3416,19 @@
         <v>17.7929</v>
       </c>
       <c r="B51" s="9" t="n">
-        <v>0.0007718397</v>
+        <v>0.0007896831</v>
       </c>
       <c r="C51" s="8" t="n">
         <v>17.7929</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.00059936</v>
+        <v>0.0005050662</v>
       </c>
       <c r="E51" s="8" t="n">
         <v>17.7929</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>0.0002438593</v>
+        <v>0.0004155518</v>
       </c>
     </row>
     <row r="52">
@@ -3436,19 +3436,19 @@
         <v>18.1588</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>0.0006446410000000001</v>
+        <v>0.0006569315</v>
       </c>
       <c r="C52" s="6" t="n">
         <v>18.1588</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>0.0004838423</v>
+        <v>0.000448738</v>
       </c>
       <c r="E52" s="6" t="n">
         <v>18.1588</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>0.000206906</v>
+        <v>0.0002442358</v>
       </c>
     </row>
     <row r="53">
@@ -3456,19 +3456,19 @@
         <v>18.5246</v>
       </c>
       <c r="B53" s="9" t="n">
-        <v>0.0005571662</v>
+        <v>0.0005554956</v>
       </c>
       <c r="C53" s="8" t="n">
         <v>18.5246</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.0004237382</v>
+        <v>0.0003758715</v>
       </c>
       <c r="E53" s="8" t="n">
         <v>18.5246</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>0.0001934721</v>
+        <v>0.0002545391</v>
       </c>
     </row>
     <row r="54">
@@ -3476,19 +3476,19 @@
         <v>18.8904</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>0.0004496503</v>
+        <v>0.0004530894</v>
       </c>
       <c r="C54" s="6" t="n">
         <v>18.8904</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>0.0003485691</v>
+        <v>0.0003140308</v>
       </c>
       <c r="E54" s="6" t="n">
         <v>18.8904</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>0.0001352397</v>
+        <v>0.0001386343</v>
       </c>
     </row>
     <row r="55">
@@ -3496,19 +3496,19 @@
         <v>19.2563</v>
       </c>
       <c r="B55" s="9" t="n">
-        <v>0.0003703874</v>
+        <v>0.0003786737</v>
       </c>
       <c r="C55" s="8" t="n">
         <v>19.2563</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.0003261842</v>
+        <v>0.000263668</v>
       </c>
       <c r="E55" s="8" t="n">
         <v>19.2563</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>0.0001004616</v>
+        <v>0.0001622767</v>
       </c>
     </row>
     <row r="56">
@@ -3516,19 +3516,19 @@
         <v>19.6221</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>0.0003146186</v>
+        <v>0.0003085618</v>
       </c>
       <c r="C56" s="6" t="n">
         <v>19.6221</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>0.0002759306</v>
+        <v>0.000222879</v>
       </c>
       <c r="E56" s="6" t="n">
         <v>19.6221</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>8.846287e-05</v>
+        <v>0.0001854887</v>
       </c>
     </row>
     <row r="57">
@@ -3536,19 +3536,19 @@
         <v>19.9879</v>
       </c>
       <c r="B57" s="9" t="n">
-        <v>0.0002557648</v>
+        <v>0.0002446449</v>
       </c>
       <c r="C57" s="8" t="n">
         <v>19.9879</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.0002395793</v>
+        <v>0.0001929356</v>
       </c>
       <c r="E57" s="8" t="n">
         <v>19.9879</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>6.573718e-05</v>
+        <v>0.0001837834</v>
       </c>
     </row>
     <row r="58">
@@ -3556,19 +3556,19 @@
         <v>20.3538</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>0.0002065315</v>
+        <v>0.0002101598</v>
       </c>
       <c r="C58" s="6" t="n">
         <v>20.3538</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>0.0001917868</v>
+        <v>0.0001435873</v>
       </c>
       <c r="E58" s="6" t="n">
         <v>20.3538</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>0.0001085729</v>
+        <v>0.0001335578</v>
       </c>
     </row>
     <row r="59">
@@ -3576,19 +3576,19 @@
         <v>20.7196</v>
       </c>
       <c r="B59" s="9" t="n">
-        <v>0.0001731096</v>
+        <v>0.0001602708</v>
       </c>
       <c r="C59" s="8" t="n">
         <v>20.7196</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.0001695936</v>
+        <v>0.0001232881</v>
       </c>
       <c r="E59" s="8" t="n">
         <v>20.7196</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>0.0001721762</v>
+        <v>0.0001444074</v>
       </c>
     </row>
     <row r="60">
@@ -3596,19 +3596,19 @@
         <v>21.0854</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>0.0001346714</v>
+        <v>0.0001375224</v>
       </c>
       <c r="C60" s="6" t="n">
         <v>21.0854</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>0.0001442995</v>
+        <v>0.0001025993</v>
       </c>
       <c r="E60" s="6" t="n">
         <v>21.0854</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>9.600526e-05</v>
+        <v>8.35037e-05</v>
       </c>
     </row>
     <row r="61">
@@ -3616,19 +3616,19 @@
         <v>21.4513</v>
       </c>
       <c r="B61" s="9" t="n">
-        <v>0.0001041175</v>
+        <v>0.0001223888</v>
       </c>
       <c r="C61" s="8" t="n">
         <v>21.4513</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.0001215348</v>
+        <v>7.778643000000001e-05</v>
       </c>
       <c r="E61" s="8" t="n">
         <v>21.4513</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>0.0001163349</v>
+        <v>4.730777e-05</v>
       </c>
     </row>
     <row r="62">
@@ -3636,19 +3636,19 @@
         <v>21.8171</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>8.901416e-05</v>
+        <v>8.816166e-05</v>
       </c>
       <c r="C62" s="6" t="n">
         <v>21.8171</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>9.296601e-05</v>
+        <v>8.603129e-05</v>
       </c>
       <c r="E62" s="6" t="n">
         <v>21.8171</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>4.194742e-05</v>
+        <v>5.863682e-05</v>
       </c>
     </row>
   </sheetData>

--- a/simple_simulation/eepf_plot_50.xlsx
+++ b/simple_simulation/eepf_plot_50.xlsx
@@ -663,7 +663,7 @@
         <v>0.2329</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>0.1193456</v>
+        <v>0.1161147</v>
       </c>
     </row>
     <row r="14">
@@ -671,7 +671,7 @@
         <v>0.5988</v>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.1140152</v>
+        <v>0.1100392</v>
       </c>
     </row>
     <row r="15">
@@ -679,7 +679,7 @@
         <v>0.9646</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>0.1026151</v>
+        <v>0.1017311</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +687,7 @@
         <v>1.3304</v>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.09476811</v>
+        <v>0.09416715000000001</v>
       </c>
     </row>
     <row r="17">
@@ -695,7 +695,7 @@
         <v>1.6963</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>0.08721385</v>
+        <v>0.08655395</v>
       </c>
     </row>
     <row r="18">
@@ -703,7 +703,7 @@
         <v>2.0621</v>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.07952244999999999</v>
+        <v>0.07974378999999999</v>
       </c>
     </row>
     <row r="19">
@@ -711,7 +711,7 @@
         <v>2.4279</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>0.07321133000000001</v>
+        <v>0.07337568999999999</v>
       </c>
     </row>
     <row r="20">
@@ -719,7 +719,7 @@
         <v>2.7938</v>
       </c>
       <c r="B20" s="9" t="n">
-        <v>0.06774012</v>
+        <v>0.06760395</v>
       </c>
     </row>
     <row r="21">
@@ -727,7 +727,7 @@
         <v>3.1596</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>0.06243023</v>
+        <v>0.06192567</v>
       </c>
     </row>
     <row r="22">
@@ -735,7 +735,7 @@
         <v>3.5254</v>
       </c>
       <c r="B22" s="9" t="n">
-        <v>0.05794753</v>
+        <v>0.05772167</v>
       </c>
     </row>
     <row r="23">
@@ -743,7 +743,7 @@
         <v>3.8912</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>0.05377977</v>
+        <v>0.05365</v>
       </c>
     </row>
     <row r="24">
@@ -751,7 +751,7 @@
         <v>4.2571</v>
       </c>
       <c r="B24" s="9" t="n">
-        <v>0.04907032</v>
+        <v>0.04972257</v>
       </c>
     </row>
     <row r="25">
@@ -759,7 +759,7 @@
         <v>4.6229</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>0.04528294</v>
+        <v>0.04611151</v>
       </c>
     </row>
     <row r="26">
@@ -767,7 +767,7 @@
         <v>4.9887</v>
       </c>
       <c r="B26" s="9" t="n">
-        <v>0.04256852</v>
+        <v>0.04241633</v>
       </c>
     </row>
     <row r="27">
@@ -775,7 +775,7 @@
         <v>5.3546</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>0.03943648</v>
+        <v>0.03943253</v>
       </c>
     </row>
     <row r="28">
@@ -783,7 +783,7 @@
         <v>5.7204</v>
       </c>
       <c r="B28" s="9" t="n">
-        <v>0.03637444</v>
+        <v>0.03645639</v>
       </c>
     </row>
     <row r="29">
@@ -791,7 +791,7 @@
         <v>6.0862</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>0.03374614</v>
+        <v>0.03370414</v>
       </c>
     </row>
     <row r="30">
@@ -799,7 +799,7 @@
         <v>6.4521</v>
       </c>
       <c r="B30" s="9" t="n">
-        <v>0.03112772</v>
+        <v>0.03140929</v>
       </c>
     </row>
     <row r="31">
@@ -807,7 +807,7 @@
         <v>6.8179</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>0.02879163</v>
+        <v>0.02905746</v>
       </c>
     </row>
     <row r="32">
@@ -815,7 +815,7 @@
         <v>7.1837</v>
       </c>
       <c r="B32" s="9" t="n">
-        <v>0.02686982</v>
+        <v>0.02695658</v>
       </c>
     </row>
     <row r="33">
@@ -823,7 +823,7 @@
         <v>7.5496</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>0.02487285</v>
+        <v>0.02474522</v>
       </c>
     </row>
     <row r="34">
@@ -831,7 +831,7 @@
         <v>7.9154</v>
       </c>
       <c r="B34" s="9" t="n">
-        <v>0.0230132</v>
+        <v>0.02269249</v>
       </c>
     </row>
     <row r="35">
@@ -839,7 +839,7 @@
         <v>8.2812</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>0.02109745</v>
+        <v>0.02095009</v>
       </c>
     </row>
     <row r="36">
@@ -847,7 +847,7 @@
         <v>8.6471</v>
       </c>
       <c r="B36" s="9" t="n">
-        <v>0.01935205</v>
+        <v>0.01926895</v>
       </c>
     </row>
     <row r="37">
@@ -855,7 +855,7 @@
         <v>9.0129</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>0.01805519</v>
+        <v>0.01786311</v>
       </c>
     </row>
     <row r="38">
@@ -863,7 +863,7 @@
         <v>9.3788</v>
       </c>
       <c r="B38" s="9" t="n">
-        <v>0.01650989</v>
+        <v>0.01616127</v>
       </c>
     </row>
     <row r="39">
@@ -871,7 +871,7 @@
         <v>9.7446</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>0.0149138</v>
+        <v>0.01503791</v>
       </c>
     </row>
     <row r="40">
@@ -879,7 +879,7 @@
         <v>10.1104</v>
       </c>
       <c r="B40" s="9" t="n">
-        <v>0.01355793</v>
+        <v>0.01389196</v>
       </c>
     </row>
     <row r="41">
@@ -887,7 +887,7 @@
         <v>10.4763</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.0124706</v>
+        <v>0.01260184</v>
       </c>
     </row>
     <row r="42">
@@ -895,7 +895,7 @@
         <v>10.8421</v>
       </c>
       <c r="B42" s="9" t="n">
-        <v>0.01136191</v>
+        <v>0.01142066</v>
       </c>
     </row>
     <row r="43">
@@ -903,7 +903,7 @@
         <v>11.2079</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>0.01017649</v>
+        <v>0.01038038</v>
       </c>
     </row>
     <row r="44">
@@ -911,7 +911,7 @@
         <v>11.5738</v>
       </c>
       <c r="B44" s="9" t="n">
-        <v>0.009110596</v>
+        <v>0.009404411999999999</v>
       </c>
     </row>
     <row r="45">
@@ -919,7 +919,7 @@
         <v>11.9396</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>0.008042179999999999</v>
+        <v>0.008386417</v>
       </c>
     </row>
     <row r="46">
@@ -927,7 +927,7 @@
         <v>12.3054</v>
       </c>
       <c r="B46" s="9" t="n">
-        <v>0.007092552</v>
+        <v>0.007317032</v>
       </c>
     </row>
     <row r="47">
@@ -935,7 +935,7 @@
         <v>12.6713</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>0.006329598</v>
+        <v>0.006404113</v>
       </c>
     </row>
     <row r="48">
@@ -943,7 +943,7 @@
         <v>13.0371</v>
       </c>
       <c r="B48" s="9" t="n">
-        <v>0.005487783</v>
+        <v>0.00563858</v>
       </c>
     </row>
     <row r="49">
@@ -951,7 +951,7 @@
         <v>13.4029</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>0.00480424</v>
+        <v>0.004891859</v>
       </c>
     </row>
     <row r="50">
@@ -959,7 +959,7 @@
         <v>13.7688</v>
       </c>
       <c r="B50" s="9" t="n">
-        <v>0.004153494</v>
+        <v>0.004194725</v>
       </c>
     </row>
     <row r="51">
@@ -967,7 +967,7 @@
         <v>14.1346</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>0.003554152</v>
+        <v>0.003587693</v>
       </c>
     </row>
     <row r="52">
@@ -975,7 +975,7 @@
         <v>14.5004</v>
       </c>
       <c r="B52" s="9" t="n">
-        <v>0.003176313</v>
+        <v>0.003171377</v>
       </c>
     </row>
     <row r="53">
@@ -983,7 +983,7 @@
         <v>14.8663</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>0.002784939</v>
+        <v>0.002762638</v>
       </c>
     </row>
     <row r="54">
@@ -991,7 +991,7 @@
         <v>15.2321</v>
       </c>
       <c r="B54" s="9" t="n">
-        <v>0.002448064</v>
+        <v>0.002409561</v>
       </c>
     </row>
     <row r="55">
@@ -999,7 +999,7 @@
         <v>15.5979</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>0.002124315</v>
+        <v>0.002160833</v>
       </c>
     </row>
     <row r="56">
@@ -1007,7 +1007,7 @@
         <v>15.9638</v>
       </c>
       <c r="B56" s="9" t="n">
-        <v>0.001787276</v>
+        <v>0.001865451</v>
       </c>
     </row>
     <row r="57">
@@ -1015,7 +1015,7 @@
         <v>16.3296</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>0.001530804</v>
+        <v>0.001585721</v>
       </c>
     </row>
     <row r="58">
@@ -1023,7 +1023,7 @@
         <v>16.6954</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>0.001304734</v>
+        <v>0.001341892</v>
       </c>
     </row>
     <row r="59">
@@ -1031,7 +1031,7 @@
         <v>17.0613</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>0.001101654</v>
+        <v>0.001106322</v>
       </c>
     </row>
     <row r="60">
@@ -1039,7 +1039,7 @@
         <v>17.4271</v>
       </c>
       <c r="B60" s="9" t="n">
-        <v>0.0009418916</v>
+        <v>0.0009194557</v>
       </c>
     </row>
     <row r="61">
@@ -1047,7 +1047,7 @@
         <v>17.7929</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>0.0007896831</v>
+        <v>0.0007666171</v>
       </c>
     </row>
     <row r="62">
@@ -1055,7 +1055,7 @@
         <v>18.1588</v>
       </c>
       <c r="B62" s="9" t="n">
-        <v>0.0006569315</v>
+        <v>0.0006374216</v>
       </c>
     </row>
     <row r="63">
@@ -1063,7 +1063,7 @@
         <v>18.5246</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>0.0005554956</v>
+        <v>0.0005292602</v>
       </c>
     </row>
     <row r="64">
@@ -1071,7 +1071,7 @@
         <v>18.8904</v>
       </c>
       <c r="B64" s="9" t="n">
-        <v>0.0004530894</v>
+        <v>0.0004509203</v>
       </c>
     </row>
     <row r="65">
@@ -1079,7 +1079,7 @@
         <v>19.2563</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>0.0003786737</v>
+        <v>0.000388524</v>
       </c>
     </row>
     <row r="66">
@@ -1087,7 +1087,7 @@
         <v>19.6221</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>0.0003085618</v>
+        <v>0.0003080721</v>
       </c>
     </row>
     <row r="67">
@@ -1095,7 +1095,7 @@
         <v>19.9879</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>0.0002446449</v>
+        <v>0.0002452153</v>
       </c>
     </row>
     <row r="68">
@@ -1103,7 +1103,7 @@
         <v>20.3538</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>0.0002101598</v>
+        <v>0.0002062173</v>
       </c>
     </row>
     <row r="69">
@@ -1111,7 +1111,7 @@
         <v>20.7196</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>0.0001602708</v>
+        <v>0.0001662552</v>
       </c>
     </row>
     <row r="70">
@@ -1119,7 +1119,7 @@
         <v>21.0854</v>
       </c>
       <c r="B70" s="9" t="n">
-        <v>0.0001375224</v>
+        <v>0.0001322249</v>
       </c>
     </row>
     <row r="71">
@@ -1127,7 +1127,7 @@
         <v>21.4513</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>0.0001223888</v>
+        <v>0.0001092961</v>
       </c>
     </row>
     <row r="72">
@@ -1135,7 +1135,7 @@
         <v>21.8171</v>
       </c>
       <c r="B72" s="9" t="n">
-        <v>8.816166e-05</v>
+        <v>9.624772e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>790069</t>
+          <t>866232</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
         <v>0.2329</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>0.1279314</v>
+        <v>0.1250693</v>
       </c>
     </row>
     <row r="14">
@@ -1295,7 +1295,7 @@
         <v>0.5988</v>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.1383799</v>
+        <v>0.1354555</v>
       </c>
     </row>
     <row r="15">
@@ -1303,7 +1303,7 @@
         <v>0.9646</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>0.1318458</v>
+        <v>0.1357362</v>
       </c>
     </row>
     <row r="16">
@@ -1311,7 +1311,7 @@
         <v>1.3304</v>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.1296057</v>
+        <v>0.1292634</v>
       </c>
     </row>
     <row r="17">
@@ -1319,7 +1319,7 @@
         <v>1.6963</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>0.121551</v>
+        <v>0.1200464</v>
       </c>
     </row>
     <row r="18">
@@ -1327,7 +1327,7 @@
         <v>2.0621</v>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.1136756</v>
+        <v>0.1087902</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>2.4279</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>0.09950185</v>
+        <v>0.09608048</v>
       </c>
     </row>
     <row r="20">
@@ -1343,7 +1343,7 @@
         <v>2.7938</v>
       </c>
       <c r="B20" s="9" t="n">
-        <v>0.08929126</v>
+        <v>0.0884968</v>
       </c>
     </row>
     <row r="21">
@@ -1351,7 +1351,7 @@
         <v>3.1596</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>0.08041019000000001</v>
+        <v>0.07960233</v>
       </c>
     </row>
     <row r="22">
@@ -1359,7 +1359,7 @@
         <v>3.5254</v>
       </c>
       <c r="B22" s="9" t="n">
-        <v>0.07099112</v>
+        <v>0.07069394</v>
       </c>
     </row>
     <row r="23">
@@ -1367,7 +1367,7 @@
         <v>3.8912</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>0.06157983</v>
+        <v>0.061677</v>
       </c>
     </row>
     <row r="24">
@@ -1375,7 +1375,7 @@
         <v>4.2571</v>
       </c>
       <c r="B24" s="9" t="n">
-        <v>0.05370494</v>
+        <v>0.05257103</v>
       </c>
     </row>
     <row r="25">
@@ -1383,7 +1383,7 @@
         <v>4.6229</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>0.04585523</v>
+        <v>0.04543619</v>
       </c>
     </row>
     <row r="26">
@@ -1391,7 +1391,7 @@
         <v>4.9887</v>
       </c>
       <c r="B26" s="9" t="n">
-        <v>0.04074065</v>
+        <v>0.04032067</v>
       </c>
     </row>
     <row r="27">
@@ -1399,7 +1399,7 @@
         <v>5.3546</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>0.03626734</v>
+        <v>0.03691355</v>
       </c>
     </row>
     <row r="28">
@@ -1407,7 +1407,7 @@
         <v>5.7204</v>
       </c>
       <c r="B28" s="9" t="n">
-        <v>0.03152257</v>
+        <v>0.03368628</v>
       </c>
     </row>
     <row r="29">
@@ -1415,7 +1415,7 @@
         <v>6.0862</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>0.02802176</v>
+        <v>0.02899618</v>
       </c>
     </row>
     <row r="30">
@@ -1423,7 +1423,7 @@
         <v>6.4521</v>
       </c>
       <c r="B30" s="9" t="n">
-        <v>0.02526826</v>
+        <v>0.02521775</v>
       </c>
     </row>
     <row r="31">
@@ -1431,7 +1431,7 @@
         <v>6.8179</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>0.02293988</v>
+        <v>0.02307792</v>
       </c>
     </row>
     <row r="32">
@@ -1439,7 +1439,7 @@
         <v>7.1837</v>
       </c>
       <c r="B32" s="9" t="n">
-        <v>0.02010311</v>
+        <v>0.02042577</v>
       </c>
     </row>
     <row r="33">
@@ -1447,7 +1447,7 @@
         <v>7.5496</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>0.0180769</v>
+        <v>0.01829224</v>
       </c>
     </row>
     <row r="34">
@@ -1455,7 +1455,7 @@
         <v>7.9154</v>
       </c>
       <c r="B34" s="9" t="n">
-        <v>0.01665564</v>
+        <v>0.01648817</v>
       </c>
     </row>
     <row r="35">
@@ -1463,7 +1463,7 @@
         <v>8.2812</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>0.01543613</v>
+        <v>0.01512356</v>
       </c>
     </row>
     <row r="36">
@@ -1471,7 +1471,7 @@
         <v>8.6471</v>
       </c>
       <c r="B36" s="9" t="n">
-        <v>0.01349451</v>
+        <v>0.0135672</v>
       </c>
     </row>
     <row r="37">
@@ -1479,7 +1479,7 @@
         <v>9.0129</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>0.01198776</v>
+        <v>0.01257406</v>
       </c>
     </row>
     <row r="38">
@@ -1487,7 +1487,7 @@
         <v>9.3788</v>
       </c>
       <c r="B38" s="9" t="n">
-        <v>0.01093267</v>
+        <v>0.01156463</v>
       </c>
     </row>
     <row r="39">
@@ -1495,7 +1495,7 @@
         <v>9.7446</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>0.01002192</v>
+        <v>0.01033892</v>
       </c>
     </row>
     <row r="40">
@@ -1503,7 +1503,7 @@
         <v>10.1104</v>
       </c>
       <c r="B40" s="9" t="n">
-        <v>0.008838809</v>
+        <v>0.009291213</v>
       </c>
     </row>
     <row r="41">
@@ -1511,7 +1511,7 @@
         <v>10.4763</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.008199348</v>
+        <v>0.008449768</v>
       </c>
     </row>
     <row r="42">
@@ -1519,7 +1519,7 @@
         <v>10.8421</v>
       </c>
       <c r="B42" s="9" t="n">
-        <v>0.007347586</v>
+        <v>0.00732678</v>
       </c>
     </row>
     <row r="43">
@@ -1527,7 +1527,7 @@
         <v>11.2079</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>0.006536499</v>
+        <v>0.006870074</v>
       </c>
     </row>
     <row r="44">
@@ -1535,7 +1535,7 @@
         <v>11.5738</v>
       </c>
       <c r="B44" s="9" t="n">
-        <v>0.005833626</v>
+        <v>0.006047953</v>
       </c>
     </row>
     <row r="45">
@@ -1543,7 +1543,7 @@
         <v>11.9396</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>0.005149051</v>
+        <v>0.0051413</v>
       </c>
     </row>
     <row r="46">
@@ -1551,7 +1551,7 @@
         <v>12.3054</v>
       </c>
       <c r="B46" s="9" t="n">
-        <v>0.004717413</v>
+        <v>0.004538044</v>
       </c>
     </row>
     <row r="47">
@@ -1559,7 +1559,7 @@
         <v>12.6713</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>0.004187535</v>
+        <v>0.004130169</v>
       </c>
     </row>
     <row r="48">
@@ -1567,7 +1567,7 @@
         <v>13.0371</v>
       </c>
       <c r="B48" s="9" t="n">
-        <v>0.003769542</v>
+        <v>0.003578919</v>
       </c>
     </row>
     <row r="49">
@@ -1575,7 +1575,7 @@
         <v>13.4029</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>0.003346819</v>
+        <v>0.003348415</v>
       </c>
     </row>
     <row r="50">
@@ -1583,7 +1583,7 @@
         <v>13.7688</v>
       </c>
       <c r="B50" s="9" t="n">
-        <v>0.002840871</v>
+        <v>0.002891317</v>
       </c>
     </row>
     <row r="51">
@@ -1591,7 +1591,7 @@
         <v>14.1346</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>0.002425164</v>
+        <v>0.002618233</v>
       </c>
     </row>
     <row r="52">
@@ -1599,7 +1599,7 @@
         <v>14.5004</v>
       </c>
       <c r="B52" s="9" t="n">
-        <v>0.002115093</v>
+        <v>0.002186536</v>
       </c>
     </row>
     <row r="53">
@@ -1607,7 +1607,7 @@
         <v>14.8663</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>0.001890348</v>
+        <v>0.001940567</v>
       </c>
     </row>
     <row r="54">
@@ -1615,7 +1615,7 @@
         <v>15.2321</v>
       </c>
       <c r="B54" s="9" t="n">
-        <v>0.001776087</v>
+        <v>0.001615825</v>
       </c>
     </row>
     <row r="55">
@@ -1623,7 +1623,7 @@
         <v>15.5979</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>0.001560413</v>
+        <v>0.001422281</v>
       </c>
     </row>
     <row r="56">
@@ -1631,7 +1631,7 @@
         <v>15.9638</v>
       </c>
       <c r="B56" s="9" t="n">
-        <v>0.001226834</v>
+        <v>0.001227879</v>
       </c>
     </row>
     <row r="57">
@@ -1639,7 +1639,7 @@
         <v>16.3296</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>0.001012416</v>
+        <v>0.001091234</v>
       </c>
     </row>
     <row r="58">
@@ -1647,7 +1647,7 @@
         <v>16.6954</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>0.0008681567</v>
+        <v>0.0009925655999999999</v>
       </c>
     </row>
     <row r="59">
@@ -1655,7 +1655,7 @@
         <v>17.0613</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>0.0006449376</v>
+        <v>0.0008777871</v>
       </c>
     </row>
     <row r="60">
@@ -1663,7 +1663,7 @@
         <v>17.4271</v>
       </c>
       <c r="B60" s="9" t="n">
-        <v>0.0006007903999999999</v>
+        <v>0.0006799785</v>
       </c>
     </row>
     <row r="61">
@@ -1671,7 +1671,7 @@
         <v>17.7929</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>0.0005050662</v>
+        <v>0.0005665385</v>
       </c>
     </row>
     <row r="62">
@@ -1679,7 +1679,7 @@
         <v>18.1588</v>
       </c>
       <c r="B62" s="9" t="n">
-        <v>0.000448738</v>
+        <v>0.0005459665</v>
       </c>
     </row>
     <row r="63">
@@ -1687,7 +1687,7 @@
         <v>18.5246</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>0.0003758715</v>
+        <v>0.0004413991</v>
       </c>
     </row>
     <row r="64">
@@ -1695,7 +1695,7 @@
         <v>18.8904</v>
       </c>
       <c r="B64" s="9" t="n">
-        <v>0.0003140308</v>
+        <v>0.0003440104</v>
       </c>
     </row>
     <row r="65">
@@ -1703,7 +1703,7 @@
         <v>19.2563</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>0.000263668</v>
+        <v>0.0003342438</v>
       </c>
     </row>
     <row r="66">
@@ -1711,7 +1711,7 @@
         <v>19.6221</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>0.000222879</v>
+        <v>0.000275452</v>
       </c>
     </row>
     <row r="67">
@@ -1719,7 +1719,7 @@
         <v>19.9879</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>0.0001929356</v>
+        <v>0.0002198912</v>
       </c>
     </row>
     <row r="68">
@@ -1727,7 +1727,7 @@
         <v>20.3538</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>0.0001435873</v>
+        <v>0.0001940836</v>
       </c>
     </row>
     <row r="69">
@@ -1735,7 +1735,7 @@
         <v>20.7196</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>0.0001232881</v>
+        <v>0.000165279</v>
       </c>
     </row>
     <row r="70">
@@ -1743,7 +1743,7 @@
         <v>21.0854</v>
       </c>
       <c r="B70" s="9" t="n">
-        <v>0.0001025993</v>
+        <v>0.0001252886</v>
       </c>
     </row>
     <row r="71">
@@ -1751,7 +1751,7 @@
         <v>21.4513</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>7.778643000000001e-05</v>
+        <v>0.0001201206</v>
       </c>
     </row>
     <row r="72">
@@ -1759,7 +1759,7 @@
         <v>21.8171</v>
       </c>
       <c r="B72" s="9" t="n">
-        <v>8.603129e-05</v>
+        <v>0.0001414422</v>
       </c>
     </row>
   </sheetData>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>49945</t>
+          <t>49531</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
         <v>0.2329</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>0.1172462</v>
+        <v>0.145842</v>
       </c>
     </row>
     <row r="14">
@@ -1919,7 +1919,7 @@
         <v>0.5988</v>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.1661457</v>
+        <v>0.1684296</v>
       </c>
     </row>
     <row r="15">
@@ -1927,7 +1927,7 @@
         <v>0.9646</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>0.1674882</v>
+        <v>0.1643142</v>
       </c>
     </row>
     <row r="16">
@@ -1935,7 +1935,7 @@
         <v>1.3304</v>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.1726272</v>
+        <v>0.1700866</v>
       </c>
     </row>
     <row r="17">
@@ -1943,7 +1943,7 @@
         <v>1.6963</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>0.1541865</v>
+        <v>0.1452453</v>
       </c>
     </row>
     <row r="18">
@@ -1951,7 +1951,7 @@
         <v>2.0621</v>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.1333955</v>
+        <v>0.1345414</v>
       </c>
     </row>
     <row r="19">
@@ -1959,7 +1959,7 @@
         <v>2.4279</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>0.1344311</v>
+        <v>0.1121491</v>
       </c>
     </row>
     <row r="20">
@@ -1967,7 +1967,7 @@
         <v>2.7938</v>
       </c>
       <c r="B20" s="9" t="n">
-        <v>0.09723498</v>
+        <v>0.09241804000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1975,7 +1975,7 @@
         <v>3.1596</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>0.08345118999999999</v>
+        <v>0.08743155</v>
       </c>
     </row>
     <row r="22">
@@ -1983,7 +1983,7 @@
         <v>3.5254</v>
       </c>
       <c r="B22" s="9" t="n">
-        <v>0.06879191</v>
+        <v>0.07868094</v>
       </c>
     </row>
     <row r="23">
@@ -1991,7 +1991,7 @@
         <v>3.8912</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>0.06361790000000001</v>
+        <v>0.06049543</v>
       </c>
     </row>
     <row r="24">
@@ -1999,7 +1999,7 @@
         <v>4.2571</v>
       </c>
       <c r="B24" s="9" t="n">
-        <v>0.04786724</v>
+        <v>0.04870684</v>
       </c>
     </row>
     <row r="25">
@@ -2007,7 +2007,7 @@
         <v>4.6229</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>0.0424949</v>
+        <v>0.04517251</v>
       </c>
     </row>
     <row r="26">
@@ -2015,7 +2015,7 @@
         <v>4.9887</v>
       </c>
       <c r="B26" s="9" t="n">
-        <v>0.03737557</v>
+        <v>0.03378844</v>
       </c>
     </row>
     <row r="27">
@@ -2023,7 +2023,7 @@
         <v>5.3546</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>0.02961374</v>
+        <v>0.02802971</v>
       </c>
     </row>
     <row r="28">
@@ -2031,7 +2031,7 @@
         <v>5.7204</v>
       </c>
       <c r="B28" s="9" t="n">
-        <v>0.02558221</v>
+        <v>0.02637944</v>
       </c>
     </row>
     <row r="29">
@@ -2039,7 +2039,7 @@
         <v>6.0862</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>0.02506789</v>
+        <v>0.02602224</v>
       </c>
     </row>
     <row r="30">
@@ -2047,7 +2047,7 @@
         <v>6.4521</v>
       </c>
       <c r="B30" s="9" t="n">
-        <v>0.02385085</v>
+        <v>0.02264196</v>
       </c>
     </row>
     <row r="31">
@@ -2055,7 +2055,7 @@
         <v>6.8179</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>0.02133506</v>
+        <v>0.01853496</v>
       </c>
     </row>
     <row r="32">
@@ -2063,7 +2063,7 @@
         <v>7.1837</v>
       </c>
       <c r="B32" s="9" t="n">
-        <v>0.0175965</v>
+        <v>0.01801562</v>
       </c>
     </row>
     <row r="33">
@@ -2071,7 +2071,7 @@
         <v>7.5496</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>0.01451338</v>
+        <v>0.01664877</v>
       </c>
     </row>
     <row r="34">
@@ -2079,7 +2079,7 @@
         <v>7.9154</v>
       </c>
       <c r="B34" s="9" t="n">
-        <v>0.01265538</v>
+        <v>0.012823</v>
       </c>
     </row>
     <row r="35">
@@ -2087,7 +2087,7 @@
         <v>8.2812</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>0.01096411</v>
+        <v>0.01078951</v>
       </c>
     </row>
     <row r="36">
@@ -2095,7 +2095,7 @@
         <v>8.6471</v>
       </c>
       <c r="B36" s="9" t="n">
-        <v>0.009611998</v>
+        <v>0.01005153</v>
       </c>
     </row>
     <row r="37">
@@ -2103,7 +2103,7 @@
         <v>9.0129</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>0.009396656</v>
+        <v>0.01025028</v>
       </c>
     </row>
     <row r="38">
@@ -2111,7 +2111,7 @@
         <v>9.3788</v>
       </c>
       <c r="B38" s="9" t="n">
-        <v>0.007780644</v>
+        <v>0.01013858</v>
       </c>
     </row>
     <row r="39">
@@ -2119,7 +2119,7 @@
         <v>9.7446</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>0.006931293</v>
+        <v>0.00888455</v>
       </c>
     </row>
     <row r="40">
@@ -2127,7 +2127,7 @@
         <v>10.1104</v>
       </c>
       <c r="B40" s="9" t="n">
-        <v>0.007235417</v>
+        <v>0.007731947</v>
       </c>
     </row>
     <row r="41">
@@ -2135,7 +2135,7 @@
         <v>10.4763</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0.005381743</v>
+        <v>0.005888837</v>
       </c>
     </row>
     <row r="42">
@@ -2143,7 +2143,7 @@
         <v>10.8421</v>
       </c>
       <c r="B42" s="9" t="n">
-        <v>0.005523069</v>
+        <v>0.004765136</v>
       </c>
     </row>
     <row r="43">
@@ -2151,7 +2151,7 @@
         <v>11.2079</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>0.004728617</v>
+        <v>0.004637215</v>
       </c>
     </row>
     <row r="44">
@@ -2159,7 +2159,7 @@
         <v>11.5738</v>
       </c>
       <c r="B44" s="9" t="n">
-        <v>0.003783812</v>
+        <v>0.003865034</v>
       </c>
     </row>
     <row r="45">
@@ -2167,7 +2167,7 @@
         <v>11.9396</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>0.003107136</v>
+        <v>0.00292597</v>
       </c>
     </row>
     <row r="46">
@@ -2175,7 +2175,7 @@
         <v>12.3054</v>
       </c>
       <c r="B46" s="9" t="n">
-        <v>0.002514065</v>
+        <v>0.002850649</v>
       </c>
     </row>
     <row r="47">
@@ -2183,7 +2183,7 @@
         <v>12.6713</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>0.002616001</v>
+        <v>0.002576391</v>
       </c>
     </row>
     <row r="48">
@@ -2191,7 +2191,7 @@
         <v>13.0371</v>
       </c>
       <c r="B48" s="9" t="n">
-        <v>0.001790155</v>
+        <v>0.002142156</v>
       </c>
     </row>
     <row r="49">
@@ -2199,7 +2199,7 @@
         <v>13.4029</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>0.001960065</v>
+        <v>0.001916538</v>
       </c>
     </row>
     <row r="50">
@@ -2207,7 +2207,7 @@
         <v>13.7688</v>
       </c>
       <c r="B50" s="9" t="n">
-        <v>0.001461459</v>
+        <v>0.001831349</v>
       </c>
     </row>
     <row r="51">
@@ -2215,7 +2215,7 @@
         <v>14.1346</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>0.001151024</v>
+        <v>0.00193975</v>
       </c>
     </row>
     <row r="52">
@@ -2223,7 +2223,7 @@
         <v>14.5004</v>
       </c>
       <c r="B52" s="9" t="n">
-        <v>0.001093257</v>
+        <v>0.001088139</v>
       </c>
     </row>
     <row r="53">
@@ -2231,7 +2231,7 @@
         <v>14.8663</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>0.001406479</v>
+        <v>0.0009886935999999999</v>
       </c>
     </row>
     <row r="54">
@@ -2239,7 +2239,7 @@
         <v>15.2321</v>
       </c>
       <c r="B54" s="9" t="n">
-        <v>0.0009684299</v>
+        <v>0.000764412</v>
       </c>
     </row>
     <row r="55">
@@ -2247,7 +2247,7 @@
         <v>15.5979</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>0.001026354</v>
+        <v>0.0007414057</v>
       </c>
     </row>
     <row r="56">
@@ -2255,7 +2255,7 @@
         <v>15.9638</v>
       </c>
       <c r="B56" s="9" t="n">
-        <v>0.0007403295</v>
+        <v>0.001202999</v>
       </c>
     </row>
     <row r="57">
@@ -2263,7 +2263,7 @@
         <v>16.3296</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>0.0009759863</v>
+        <v>0.0006699184</v>
       </c>
     </row>
     <row r="58">
@@ -2271,7 +2271,7 @@
         <v>16.6954</v>
       </c>
       <c r="B58" s="9" t="n">
-        <v>0.0006703014</v>
+        <v>0.0005678897</v>
       </c>
     </row>
     <row r="59">
@@ -2279,7 +2279,7 @@
         <v>17.0613</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>0.0005171993</v>
+        <v>0.0004815157</v>
       </c>
     </row>
     <row r="60">
@@ -2287,7 +2287,7 @@
         <v>17.4271</v>
       </c>
       <c r="B60" s="9" t="n">
-        <v>0.0004854988</v>
+        <v>0.0004764348</v>
       </c>
     </row>
     <row r="61">
@@ -2295,7 +2295,7 @@
         <v>17.7929</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>0.0004155518</v>
+        <v>0.0005369992</v>
       </c>
     </row>
     <row r="62">
@@ -2303,7 +2303,7 @@
         <v>18.1588</v>
       </c>
       <c r="B62" s="9" t="n">
-        <v>0.0002442358</v>
+        <v>0.0005445273</v>
       </c>
     </row>
     <row r="63">
@@ -2311,7 +2311,7 @@
         <v>18.5246</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>0.0002545391</v>
+        <v>0.0004107609</v>
       </c>
     </row>
     <row r="64">
@@ -2319,7 +2319,7 @@
         <v>18.8904</v>
       </c>
       <c r="B64" s="9" t="n">
-        <v>0.0001386343</v>
+        <v>0.0006355688</v>
       </c>
     </row>
     <row r="65">
@@ -2327,7 +2327,7 @@
         <v>19.2563</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>0.0001622767</v>
+        <v>0.0004280618</v>
       </c>
     </row>
     <row r="66">
@@ -2335,7 +2335,7 @@
         <v>19.6221</v>
       </c>
       <c r="B66" s="9" t="n">
-        <v>0.0001854887</v>
+        <v>0.0003118034</v>
       </c>
     </row>
     <row r="67">
@@ -2343,7 +2343,7 @@
         <v>19.9879</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>0.0001837834</v>
+        <v>0.0003583667</v>
       </c>
     </row>
     <row r="68">
@@ -2351,7 +2351,7 @@
         <v>20.3538</v>
       </c>
       <c r="B68" s="9" t="n">
-        <v>0.0001335578</v>
+        <v>0.0002694101</v>
       </c>
     </row>
     <row r="69">
@@ -2359,7 +2359,7 @@
         <v>20.7196</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>0.0001444074</v>
+        <v>4.854929e-05</v>
       </c>
     </row>
     <row r="70">
@@ -2367,7 +2367,7 @@
         <v>21.0854</v>
       </c>
       <c r="B70" s="9" t="n">
-        <v>8.35037e-05</v>
+        <v>3.609471e-05</v>
       </c>
     </row>
     <row r="71">
@@ -2375,7 +2375,7 @@
         <v>21.4513</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>4.730777e-05</v>
+        <v>3.57856e-05</v>
       </c>
     </row>
     <row r="72">
@@ -2383,7 +2383,7 @@
         <v>21.8171</v>
       </c>
       <c r="B72" s="9" t="n">
-        <v>5.863682e-05</v>
+        <v>3.54843e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2456,19 +2456,19 @@
         <v>0.2329</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>0.1193456</v>
+        <v>0.1161147</v>
       </c>
       <c r="C3" s="8" t="n">
         <v>0.2329</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.1279314</v>
+        <v>0.1250693</v>
       </c>
       <c r="E3" s="8" t="n">
         <v>0.2329</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>0.1172462</v>
+        <v>0.145842</v>
       </c>
     </row>
     <row r="4">
@@ -2476,19 +2476,19 @@
         <v>0.5988</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>0.1140152</v>
+        <v>0.1100392</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>0.5988</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>0.1383799</v>
+        <v>0.1354555</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>0.5988</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>0.1661457</v>
+        <v>0.1684296</v>
       </c>
     </row>
     <row r="5">
@@ -2496,19 +2496,19 @@
         <v>0.9646</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.1026151</v>
+        <v>0.1017311</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>0.9646</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.1318458</v>
+        <v>0.1357362</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>0.9646</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>0.1674882</v>
+        <v>0.1643142</v>
       </c>
     </row>
     <row r="6">
@@ -2516,19 +2516,19 @@
         <v>1.3304</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>0.09476811</v>
+        <v>0.09416715000000001</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>1.3304</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>0.1296057</v>
+        <v>0.1292634</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>1.3304</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>0.1726272</v>
+        <v>0.1700866</v>
       </c>
     </row>
     <row r="7">
@@ -2536,19 +2536,19 @@
         <v>1.6963</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>0.08721385</v>
+        <v>0.08655395</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>1.6963</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.121551</v>
+        <v>0.1200464</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>1.6963</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>0.1541865</v>
+        <v>0.1452453</v>
       </c>
     </row>
     <row r="8">
@@ -2556,19 +2556,19 @@
         <v>2.0621</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>0.07952244999999999</v>
+        <v>0.07974378999999999</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>2.0621</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0.1136756</v>
+        <v>0.1087902</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>2.0621</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>0.1333955</v>
+        <v>0.1345414</v>
       </c>
     </row>
     <row r="9">
@@ -2576,19 +2576,19 @@
         <v>2.4279</v>
       </c>
       <c r="B9" s="9" t="n">
-        <v>0.07321133000000001</v>
+        <v>0.07337568999999999</v>
       </c>
       <c r="C9" s="8" t="n">
         <v>2.4279</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.09950185</v>
+        <v>0.09608048</v>
       </c>
       <c r="E9" s="8" t="n">
         <v>2.4279</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>0.1344311</v>
+        <v>0.1121491</v>
       </c>
     </row>
     <row r="10">
@@ -2596,19 +2596,19 @@
         <v>2.7938</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.06774012</v>
+        <v>0.06760395</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>2.7938</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0.08929126</v>
+        <v>0.0884968</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>2.7938</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>0.09723498</v>
+        <v>0.09241804000000001</v>
       </c>
     </row>
     <row r="11">
@@ -2616,19 +2616,19 @@
         <v>3.1596</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>0.06243023</v>
+        <v>0.06192567</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>3.1596</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.08041019000000001</v>
+        <v>0.07960233</v>
       </c>
       <c r="E11" s="8" t="n">
         <v>3.1596</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>0.08345118999999999</v>
+        <v>0.08743155</v>
       </c>
     </row>
     <row r="12">
@@ -2636,19 +2636,19 @@
         <v>3.5254</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>0.05794753</v>
+        <v>0.05772167</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>3.5254</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.07099112</v>
+        <v>0.07069394</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>3.5254</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>0.06879191</v>
+        <v>0.07868094</v>
       </c>
     </row>
     <row r="13">
@@ -2656,19 +2656,19 @@
         <v>3.8912</v>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.05377977</v>
+        <v>0.05365</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>3.8912</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.06157983</v>
+        <v>0.061677</v>
       </c>
       <c r="E13" s="8" t="n">
         <v>3.8912</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>0.06361790000000001</v>
+        <v>0.06049543</v>
       </c>
     </row>
     <row r="14">
@@ -2676,19 +2676,19 @@
         <v>4.2571</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>0.04907032</v>
+        <v>0.04972257</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>4.2571</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.05370494</v>
+        <v>0.05257103</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>4.2571</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0.04786724</v>
+        <v>0.04870684</v>
       </c>
     </row>
     <row r="15">
@@ -2696,19 +2696,19 @@
         <v>4.6229</v>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.04528294</v>
+        <v>0.04611151</v>
       </c>
       <c r="C15" s="8" t="n">
         <v>4.6229</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.04585523</v>
+        <v>0.04543619</v>
       </c>
       <c r="E15" s="8" t="n">
         <v>4.6229</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>0.0424949</v>
+        <v>0.04517251</v>
       </c>
     </row>
     <row r="16">
@@ -2716,19 +2716,19 @@
         <v>4.9887</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>0.04256852</v>
+        <v>0.04241633</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>4.9887</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.04074065</v>
+        <v>0.04032067</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>4.9887</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>0.03737557</v>
+        <v>0.03378844</v>
       </c>
     </row>
     <row r="17">
@@ -2736,19 +2736,19 @@
         <v>5.3546</v>
       </c>
       <c r="B17" s="9" t="n">
-        <v>0.03943648</v>
+        <v>0.03943253</v>
       </c>
       <c r="C17" s="8" t="n">
         <v>5.3546</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.03626734</v>
+        <v>0.03691355</v>
       </c>
       <c r="E17" s="8" t="n">
         <v>5.3546</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>0.02961374</v>
+        <v>0.02802971</v>
       </c>
     </row>
     <row r="18">
@@ -2756,19 +2756,19 @@
         <v>5.7204</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>0.03637444</v>
+        <v>0.03645639</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>5.7204</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.03152257</v>
+        <v>0.03368628</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>5.7204</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>0.02558221</v>
+        <v>0.02637944</v>
       </c>
     </row>
     <row r="19">
@@ -2776,19 +2776,19 @@
         <v>6.0862</v>
       </c>
       <c r="B19" s="9" t="n">
-        <v>0.03374614</v>
+        <v>0.03370414</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>6.0862</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.02802176</v>
+        <v>0.02899618</v>
       </c>
       <c r="E19" s="8" t="n">
         <v>6.0862</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>0.02506789</v>
+        <v>0.02602224</v>
       </c>
     </row>
     <row r="20">
@@ -2796,19 +2796,19 @@
         <v>6.4521</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>0.03112772</v>
+        <v>0.03140929</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>6.4521</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.02526826</v>
+        <v>0.02521775</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>6.4521</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.02385085</v>
+        <v>0.02264196</v>
       </c>
     </row>
     <row r="21">
@@ -2816,19 +2816,19 @@
         <v>6.8179</v>
       </c>
       <c r="B21" s="9" t="n">
-        <v>0.02879163</v>
+        <v>0.02905746</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>6.8179</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.02293988</v>
+        <v>0.02307792</v>
       </c>
       <c r="E21" s="8" t="n">
         <v>6.8179</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>0.02133506</v>
+        <v>0.01853496</v>
       </c>
     </row>
     <row r="22">
@@ -2836,19 +2836,19 @@
         <v>7.1837</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>0.02686982</v>
+        <v>0.02695658</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>7.1837</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.02010311</v>
+        <v>0.02042577</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>7.1837</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0175965</v>
+        <v>0.01801562</v>
       </c>
     </row>
     <row r="23">
@@ -2856,19 +2856,19 @@
         <v>7.5496</v>
       </c>
       <c r="B23" s="9" t="n">
-        <v>0.02487285</v>
+        <v>0.02474522</v>
       </c>
       <c r="C23" s="8" t="n">
         <v>7.5496</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.0180769</v>
+        <v>0.01829224</v>
       </c>
       <c r="E23" s="8" t="n">
         <v>7.5496</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>0.01451338</v>
+        <v>0.01664877</v>
       </c>
     </row>
     <row r="24">
@@ -2876,19 +2876,19 @@
         <v>7.9154</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>0.0230132</v>
+        <v>0.02269249</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>7.9154</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.01665564</v>
+        <v>0.01648817</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>7.9154</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.01265538</v>
+        <v>0.012823</v>
       </c>
     </row>
     <row r="25">
@@ -2896,19 +2896,19 @@
         <v>8.2812</v>
       </c>
       <c r="B25" s="9" t="n">
-        <v>0.02109745</v>
+        <v>0.02095009</v>
       </c>
       <c r="C25" s="8" t="n">
         <v>8.2812</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.01543613</v>
+        <v>0.01512356</v>
       </c>
       <c r="E25" s="8" t="n">
         <v>8.2812</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>0.01096411</v>
+        <v>0.01078951</v>
       </c>
     </row>
     <row r="26">
@@ -2916,19 +2916,19 @@
         <v>8.6471</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>0.01935205</v>
+        <v>0.01926895</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>8.6471</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>0.01349451</v>
+        <v>0.0135672</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>8.6471</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>0.009611998</v>
+        <v>0.01005153</v>
       </c>
     </row>
     <row r="27">
@@ -2936,19 +2936,19 @@
         <v>9.0129</v>
       </c>
       <c r="B27" s="9" t="n">
-        <v>0.01805519</v>
+        <v>0.01786311</v>
       </c>
       <c r="C27" s="8" t="n">
         <v>9.0129</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.01198776</v>
+        <v>0.01257406</v>
       </c>
       <c r="E27" s="8" t="n">
         <v>9.0129</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>0.009396656</v>
+        <v>0.01025028</v>
       </c>
     </row>
     <row r="28">
@@ -2956,19 +2956,19 @@
         <v>9.3788</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>0.01650989</v>
+        <v>0.01616127</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>9.3788</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>0.01093267</v>
+        <v>0.01156463</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>9.3788</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>0.007780644</v>
+        <v>0.01013858</v>
       </c>
     </row>
     <row r="29">
@@ -2976,19 +2976,19 @@
         <v>9.7446</v>
       </c>
       <c r="B29" s="9" t="n">
-        <v>0.0149138</v>
+        <v>0.01503791</v>
       </c>
       <c r="C29" s="8" t="n">
         <v>9.7446</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.01002192</v>
+        <v>0.01033892</v>
       </c>
       <c r="E29" s="8" t="n">
         <v>9.7446</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>0.006931293</v>
+        <v>0.00888455</v>
       </c>
     </row>
     <row r="30">
@@ -2996,19 +2996,19 @@
         <v>10.1104</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>0.01355793</v>
+        <v>0.01389196</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>10.1104</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>0.008838809</v>
+        <v>0.009291213</v>
       </c>
       <c r="E30" s="6" t="n">
         <v>10.1104</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>0.007235417</v>
+        <v>0.007731947</v>
       </c>
     </row>
     <row r="31">
@@ -3016,19 +3016,19 @@
         <v>10.4763</v>
       </c>
       <c r="B31" s="9" t="n">
-        <v>0.0124706</v>
+        <v>0.01260184</v>
       </c>
       <c r="C31" s="8" t="n">
         <v>10.4763</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.008199348</v>
+        <v>0.008449768</v>
       </c>
       <c r="E31" s="8" t="n">
         <v>10.4763</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>0.005381743</v>
+        <v>0.005888837</v>
       </c>
     </row>
     <row r="32">
@@ -3036,19 +3036,19 @@
         <v>10.8421</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>0.01136191</v>
+        <v>0.01142066</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>10.8421</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>0.007347586</v>
+        <v>0.00732678</v>
       </c>
       <c r="E32" s="6" t="n">
         <v>10.8421</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>0.005523069</v>
+        <v>0.004765136</v>
       </c>
     </row>
     <row r="33">
@@ -3056,19 +3056,19 @@
         <v>11.2079</v>
       </c>
       <c r="B33" s="9" t="n">
-        <v>0.01017649</v>
+        <v>0.01038038</v>
       </c>
       <c r="C33" s="8" t="n">
         <v>11.2079</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.006536499</v>
+        <v>0.006870074</v>
       </c>
       <c r="E33" s="8" t="n">
         <v>11.2079</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>0.004728617</v>
+        <v>0.004637215</v>
       </c>
     </row>
     <row r="34">
@@ -3076,19 +3076,19 @@
         <v>11.5738</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>0.009110596</v>
+        <v>0.009404411999999999</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>11.5738</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>0.005833626</v>
+        <v>0.006047953</v>
       </c>
       <c r="E34" s="6" t="n">
         <v>11.5738</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>0.003783812</v>
+        <v>0.003865034</v>
       </c>
     </row>
     <row r="35">
@@ -3096,19 +3096,19 @@
         <v>11.9396</v>
       </c>
       <c r="B35" s="9" t="n">
-        <v>0.008042179999999999</v>
+        <v>0.008386417</v>
       </c>
       <c r="C35" s="8" t="n">
         <v>11.9396</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.005149051</v>
+        <v>0.0051413</v>
       </c>
       <c r="E35" s="8" t="n">
         <v>11.9396</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>0.003107136</v>
+        <v>0.00292597</v>
       </c>
     </row>
     <row r="36">
@@ -3116,19 +3116,19 @@
         <v>12.3054</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>0.007092552</v>
+        <v>0.007317032</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>12.3054</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>0.004717413</v>
+        <v>0.004538044</v>
       </c>
       <c r="E36" s="6" t="n">
         <v>12.3054</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>0.002514065</v>
+        <v>0.002850649</v>
       </c>
     </row>
     <row r="37">
@@ -3136,19 +3136,19 @@
         <v>12.6713</v>
       </c>
       <c r="B37" s="9" t="n">
-        <v>0.006329598</v>
+        <v>0.006404113</v>
       </c>
       <c r="C37" s="8" t="n">
         <v>12.6713</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.004187535</v>
+        <v>0.004130169</v>
       </c>
       <c r="E37" s="8" t="n">
         <v>12.6713</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>0.002616001</v>
+        <v>0.002576391</v>
       </c>
     </row>
     <row r="38">
@@ -3156,19 +3156,19 @@
         <v>13.0371</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>0.005487783</v>
+        <v>0.00563858</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>13.0371</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>0.003769542</v>
+        <v>0.003578919</v>
       </c>
       <c r="E38" s="6" t="n">
         <v>13.0371</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>0.001790155</v>
+        <v>0.002142156</v>
       </c>
     </row>
     <row r="39">
@@ -3176,19 +3176,19 @@
         <v>13.4029</v>
       </c>
       <c r="B39" s="9" t="n">
-        <v>0.00480424</v>
+        <v>0.004891859</v>
       </c>
       <c r="C39" s="8" t="n">
         <v>13.4029</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.003346819</v>
+        <v>0.003348415</v>
       </c>
       <c r="E39" s="8" t="n">
         <v>13.4029</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>0.001960065</v>
+        <v>0.001916538</v>
       </c>
     </row>
     <row r="40">
@@ -3196,19 +3196,19 @@
         <v>13.7688</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>0.004153494</v>
+        <v>0.004194725</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>13.7688</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>0.002840871</v>
+        <v>0.002891317</v>
       </c>
       <c r="E40" s="6" t="n">
         <v>13.7688</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>0.001461459</v>
+        <v>0.001831349</v>
       </c>
     </row>
     <row r="41">
@@ -3216,19 +3216,19 @@
         <v>14.1346</v>
       </c>
       <c r="B41" s="9" t="n">
-        <v>0.003554152</v>
+        <v>0.003587693</v>
       </c>
       <c r="C41" s="8" t="n">
         <v>14.1346</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.002425164</v>
+        <v>0.002618233</v>
       </c>
       <c r="E41" s="8" t="n">
         <v>14.1346</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>0.001151024</v>
+        <v>0.00193975</v>
       </c>
     </row>
     <row r="42">
@@ -3236,19 +3236,19 @@
         <v>14.5004</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>0.003176313</v>
+        <v>0.003171377</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>14.5004</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>0.002115093</v>
+        <v>0.002186536</v>
       </c>
       <c r="E42" s="6" t="n">
         <v>14.5004</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>0.001093257</v>
+        <v>0.001088139</v>
       </c>
     </row>
     <row r="43">
@@ -3256,19 +3256,19 @@
         <v>14.8663</v>
       </c>
       <c r="B43" s="9" t="n">
-        <v>0.002784939</v>
+        <v>0.002762638</v>
       </c>
       <c r="C43" s="8" t="n">
         <v>14.8663</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.001890348</v>
+        <v>0.001940567</v>
       </c>
       <c r="E43" s="8" t="n">
         <v>14.8663</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>0.001406479</v>
+        <v>0.0009886935999999999</v>
       </c>
     </row>
     <row r="44">
@@ -3276,19 +3276,19 @@
         <v>15.2321</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>0.002448064</v>
+        <v>0.002409561</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>15.2321</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>0.001776087</v>
+        <v>0.001615825</v>
       </c>
       <c r="E44" s="6" t="n">
         <v>15.2321</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>0.0009684299</v>
+        <v>0.000764412</v>
       </c>
     </row>
     <row r="45">
@@ -3296,19 +3296,19 @@
         <v>15.5979</v>
       </c>
       <c r="B45" s="9" t="n">
-        <v>0.002124315</v>
+        <v>0.002160833</v>
       </c>
       <c r="C45" s="8" t="n">
         <v>15.5979</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.001560413</v>
+        <v>0.001422281</v>
       </c>
       <c r="E45" s="8" t="n">
         <v>15.5979</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>0.001026354</v>
+        <v>0.0007414057</v>
       </c>
     </row>
     <row r="46">
@@ -3316,19 +3316,19 @@
         <v>15.9638</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>0.001787276</v>
+        <v>0.001865451</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>15.9638</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>0.001226834</v>
+        <v>0.001227879</v>
       </c>
       <c r="E46" s="6" t="n">
         <v>15.9638</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>0.0007403295</v>
+        <v>0.001202999</v>
       </c>
     </row>
     <row r="47">
@@ -3336,19 +3336,19 @@
         <v>16.3296</v>
       </c>
       <c r="B47" s="9" t="n">
-        <v>0.001530804</v>
+        <v>0.001585721</v>
       </c>
       <c r="C47" s="8" t="n">
         <v>16.3296</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.001012416</v>
+        <v>0.001091234</v>
       </c>
       <c r="E47" s="8" t="n">
         <v>16.3296</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>0.0009759863</v>
+        <v>0.0006699184</v>
       </c>
     </row>
     <row r="48">
@@ -3356,19 +3356,19 @@
         <v>16.6954</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>0.001304734</v>
+        <v>0.001341892</v>
       </c>
       <c r="C48" s="6" t="n">
         <v>16.6954</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>0.0008681567</v>
+        <v>0.0009925655999999999</v>
       </c>
       <c r="E48" s="6" t="n">
         <v>16.6954</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>0.0006703014</v>
+        <v>0.0005678897</v>
       </c>
     </row>
     <row r="49">
@@ -3376,19 +3376,19 @@
         <v>17.0613</v>
       </c>
       <c r="B49" s="9" t="n">
-        <v>0.001101654</v>
+        <v>0.001106322</v>
       </c>
       <c r="C49" s="8" t="n">
         <v>17.0613</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.0006449376</v>
+        <v>0.0008777871</v>
       </c>
       <c r="E49" s="8" t="n">
         <v>17.0613</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>0.0005171993</v>
+        <v>0.0004815157</v>
       </c>
     </row>
     <row r="50">
@@ -3396,19 +3396,19 @@
         <v>17.4271</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>0.0009418916</v>
+        <v>0.0009194557</v>
       </c>
       <c r="C50" s="6" t="n">
         <v>17.4271</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>0.0006007903999999999</v>
+        <v>0.0006799785</v>
       </c>
       <c r="E50" s="6" t="n">
         <v>17.4271</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>0.0004854988</v>
+        <v>0.0004764348</v>
       </c>
     </row>
     <row r="51">
@@ -3416,19 +3416,19 @@
         <v>17.7929</v>
       </c>
       <c r="B51" s="9" t="n">
-        <v>0.0007896831</v>
+        <v>0.0007666171</v>
       </c>
       <c r="C51" s="8" t="n">
         <v>17.7929</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.0005050662</v>
+        <v>0.0005665385</v>
       </c>
       <c r="E51" s="8" t="n">
         <v>17.7929</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>0.0004155518</v>
+        <v>0.0005369992</v>
       </c>
     </row>
     <row r="52">
@@ -3436,19 +3436,19 @@
         <v>18.1588</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>0.0006569315</v>
+        <v>0.0006374216</v>
       </c>
       <c r="C52" s="6" t="n">
         <v>18.1588</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>0.000448738</v>
+        <v>0.0005459665</v>
       </c>
       <c r="E52" s="6" t="n">
         <v>18.1588</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>0.0002442358</v>
+        <v>0.0005445273</v>
       </c>
     </row>
     <row r="53">
@@ -3456,19 +3456,19 @@
         <v>18.5246</v>
       </c>
       <c r="B53" s="9" t="n">
-        <v>0.0005554956</v>
+        <v>0.0005292602</v>
       </c>
       <c r="C53" s="8" t="n">
         <v>18.5246</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.0003758715</v>
+        <v>0.0004413991</v>
       </c>
       <c r="E53" s="8" t="n">
         <v>18.5246</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>0.0002545391</v>
+        <v>0.0004107609</v>
       </c>
     </row>
     <row r="54">
@@ -3476,19 +3476,19 @@
         <v>18.8904</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>0.0004530894</v>
+        <v>0.0004509203</v>
       </c>
       <c r="C54" s="6" t="n">
         <v>18.8904</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>0.0003140308</v>
+        <v>0.0003440104</v>
       </c>
       <c r="E54" s="6" t="n">
         <v>18.8904</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>0.0001386343</v>
+        <v>0.0006355688</v>
       </c>
     </row>
     <row r="55">
@@ -3496,19 +3496,19 @@
         <v>19.2563</v>
       </c>
       <c r="B55" s="9" t="n">
-        <v>0.0003786737</v>
+        <v>0.000388524</v>
       </c>
       <c r="C55" s="8" t="n">
         <v>19.2563</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.000263668</v>
+        <v>0.0003342438</v>
       </c>
       <c r="E55" s="8" t="n">
         <v>19.2563</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>0.0001622767</v>
+        <v>0.0004280618</v>
       </c>
     </row>
     <row r="56">
@@ -3516,19 +3516,19 @@
         <v>19.6221</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>0.0003085618</v>
+        <v>0.0003080721</v>
       </c>
       <c r="C56" s="6" t="n">
         <v>19.6221</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>0.000222879</v>
+        <v>0.000275452</v>
       </c>
       <c r="E56" s="6" t="n">
         <v>19.6221</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>0.0001854887</v>
+        <v>0.0003118034</v>
       </c>
     </row>
     <row r="57">
@@ -3536,19 +3536,19 @@
         <v>19.9879</v>
       </c>
       <c r="B57" s="9" t="n">
-        <v>0.0002446449</v>
+        <v>0.0002452153</v>
       </c>
       <c r="C57" s="8" t="n">
         <v>19.9879</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.0001929356</v>
+        <v>0.0002198912</v>
       </c>
       <c r="E57" s="8" t="n">
         <v>19.9879</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>0.0001837834</v>
+        <v>0.0003583667</v>
       </c>
     </row>
     <row r="58">
@@ -3556,19 +3556,19 @@
         <v>20.3538</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>0.0002101598</v>
+        <v>0.0002062173</v>
       </c>
       <c r="C58" s="6" t="n">
         <v>20.3538</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>0.0001435873</v>
+        <v>0.0001940836</v>
       </c>
       <c r="E58" s="6" t="n">
         <v>20.3538</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>0.0001335578</v>
+        <v>0.0002694101</v>
       </c>
     </row>
     <row r="59">
@@ -3576,19 +3576,19 @@
         <v>20.7196</v>
       </c>
       <c r="B59" s="9" t="n">
-        <v>0.0001602708</v>
+        <v>0.0001662552</v>
       </c>
       <c r="C59" s="8" t="n">
         <v>20.7196</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.0001232881</v>
+        <v>0.000165279</v>
       </c>
       <c r="E59" s="8" t="n">
         <v>20.7196</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>0.0001444074</v>
+        <v>4.854929e-05</v>
       </c>
     </row>
     <row r="60">
@@ -3596,19 +3596,19 @@
         <v>21.0854</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>0.0001375224</v>
+        <v>0.0001322249</v>
       </c>
       <c r="C60" s="6" t="n">
         <v>21.0854</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>0.0001025993</v>
+        <v>0.0001252886</v>
       </c>
       <c r="E60" s="6" t="n">
         <v>21.0854</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>8.35037e-05</v>
+        <v>3.609471e-05</v>
       </c>
     </row>
     <row r="61">
@@ -3616,19 +3616,19 @@
         <v>21.4513</v>
       </c>
       <c r="B61" s="9" t="n">
-        <v>0.0001223888</v>
+        <v>0.0001092961</v>
       </c>
       <c r="C61" s="8" t="n">
         <v>21.4513</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>7.778643000000001e-05</v>
+        <v>0.0001201206</v>
       </c>
       <c r="E61" s="8" t="n">
         <v>21.4513</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>4.730777e-05</v>
+        <v>3.57856e-05</v>
       </c>
     </row>
     <row r="62">
@@ -3636,19 +3636,19 @@
         <v>21.8171</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>8.816166e-05</v>
+        <v>9.624772e-05</v>
       </c>
       <c r="C62" s="6" t="n">
         <v>21.8171</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>8.603129e-05</v>
+        <v>0.0001414422</v>
       </c>
       <c r="E62" s="6" t="n">
         <v>21.8171</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>5.863682e-05</v>
+        <v>3.54843e-05</v>
       </c>
     </row>
   </sheetData>
